--- a/Dynamic_programming.xlsx
+++ b/Dynamic_programming.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/adma24ac_student_cbs_dk/Documents/Skrivebord/Operationsanalyse/Eksamen/OA_HA_MAT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="474" documentId="11_AD4D1D646341095ACB7000FE0597FE22683EDF0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3105C7A5-07AC-4927-A496-87DACB0DBF1C}"/>
+  <xr:revisionPtr revIDLastSave="1604" documentId="11_AD4D1D646341095ACB7000FE0597FE22683EDF0E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F679A83-5CD1-47B8-8E72-A46F052019FD}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
     <sheet name="Shortest path" sheetId="2" r:id="rId2"/>
-    <sheet name="Lagertoeri" sheetId="3" r:id="rId3"/>
+    <sheet name="Lagertoeri (shit)" sheetId="3" r:id="rId3"/>
+    <sheet name="Lagerteori axelotl" sheetId="4" r:id="rId4"/>
+    <sheet name="bedste indtil videre" sheetId="5" r:id="rId5"/>
+    <sheet name="Neckarwestheim" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="120">
   <si>
     <t>Længde i</t>
   </si>
@@ -127,6 +130,9 @@
     <t>A -&gt; D -&gt; F -&gt; I  -&gt; J</t>
   </si>
   <si>
+    <t>Informationsoversigt</t>
+  </si>
+  <si>
     <t>Produktionsomkostninger pr. enhed produceret</t>
   </si>
   <si>
@@ -209,6 +215,192 @@
   </si>
   <si>
     <t>Season 1</t>
+  </si>
+  <si>
+    <t>Maks køb pr. dag</t>
+  </si>
+  <si>
+    <t>Faste omkostnigner ved køb</t>
+  </si>
+  <si>
+    <t>stk</t>
+  </si>
+  <si>
+    <t>kroner</t>
+  </si>
+  <si>
+    <t>Maks lagerplads</t>
+  </si>
+  <si>
+    <t>Faste lageromkostninger</t>
+  </si>
+  <si>
+    <t>Variable lageromkostninger</t>
+  </si>
+  <si>
+    <t>Startlager</t>
+  </si>
+  <si>
+    <t>Efterspørgsel</t>
+  </si>
+  <si>
+    <t>Periode</t>
+  </si>
+  <si>
+    <t>efterspørgsel</t>
+  </si>
+  <si>
+    <t>Nødvendig produktion</t>
+  </si>
+  <si>
+    <t>Variable omkostnigner</t>
+  </si>
+  <si>
+    <t>Faste omkostninger</t>
+  </si>
+  <si>
+    <t>Omkostninger i alt</t>
+  </si>
+  <si>
+    <t>Case 1</t>
+  </si>
+  <si>
+    <t>Case 2</t>
+  </si>
+  <si>
+    <t>Case 3</t>
+  </si>
+  <si>
+    <t>Case 4</t>
+  </si>
+  <si>
+    <t>Minimum omkostning</t>
+  </si>
+  <si>
+    <t>Optimal produktionsplan</t>
+  </si>
+  <si>
+    <t>Periode 1</t>
+  </si>
+  <si>
+    <t>Periode 2</t>
+  </si>
+  <si>
+    <t>Periode 3</t>
+  </si>
+  <si>
+    <t>Maks prod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antal prod af gangen </t>
+  </si>
+  <si>
+    <t>euro</t>
+  </si>
+  <si>
+    <t>Euro</t>
+  </si>
+  <si>
+    <t>Stk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variable omkostninger </t>
+  </si>
+  <si>
+    <t>Pr. måned</t>
+  </si>
+  <si>
+    <t>Pr. stk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lagerkapacitet </t>
+  </si>
+  <si>
+    <t>Informationsoversigt:</t>
+  </si>
+  <si>
+    <t>Måned</t>
+  </si>
+  <si>
+    <t>Stage</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>Maj</t>
+  </si>
+  <si>
+    <t>Juni</t>
+  </si>
+  <si>
+    <t>Juli</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
+  <si>
+    <t>Stage 5</t>
+  </si>
+  <si>
+    <t>Samlede omkostninger</t>
+  </si>
+  <si>
+    <t>Maks prod overholdt?</t>
+  </si>
+  <si>
+    <t>Maks kap overholdt</t>
+  </si>
+  <si>
+    <t>Næste periode</t>
+  </si>
+  <si>
+    <t>Forrige periode</t>
+  </si>
+  <si>
+    <t>Minimums oversigt</t>
+  </si>
+  <si>
+    <t>Minimale omkostninger</t>
+  </si>
+  <si>
+    <t>Case 5</t>
+  </si>
+  <si>
+    <t>Optimale produktionsplan</t>
+  </si>
+  <si>
+    <t>Isar 2</t>
+  </si>
+  <si>
+    <t>Brokdorf</t>
+  </si>
+  <si>
+    <t>Neckawestheim</t>
+  </si>
+  <si>
+    <t>Hold til næste stage</t>
+  </si>
+  <si>
+    <t>Hold fra forrige stage</t>
+  </si>
+  <si>
+    <t>Profit denne stage</t>
+  </si>
+  <si>
+    <t>Hold denne stage</t>
+  </si>
+  <si>
+    <t>Hold til denne stage/hold til næste stage</t>
+  </si>
+  <si>
+    <t>Hold næste stage</t>
+  </si>
+  <si>
+    <t>Optimal holdfordeling</t>
+  </si>
+  <si>
+    <t>Antal hold</t>
   </si>
 </sst>
 </file>
@@ -218,7 +410,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;kr.&quot;_-;\-* #,##0.00\ &quot;kr.&quot;_-;_-* &quot;-&quot;??\ &quot;kr.&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,13 +433,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -261,8 +479,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -439,17 +681,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -457,7 +732,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -466,14 +741,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
@@ -481,9 +753,70 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -549,6 +882,114 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>86783</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C7D80CEC-B7AD-C000-EE31-2A4E9FC08B2D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="5953125" cy="3962400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>374043</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>128132</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1007985</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>116911</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C11DBE20-2E12-1D17-04FD-05AA81511D83}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="374043" y="128132"/>
+          <a:ext cx="4844079" cy="1458847"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -977,376 +1418,280 @@
   </cols>
   <sheetData>
     <row r="3" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="H3" s="3" t="s">
+      <c r="H3" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
     </row>
     <row r="4" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="H4" s="3" t="s">
+      <c r="H4" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
       <c r="P4" s="2"/>
     </row>
     <row r="5" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="H5" s="3" t="s">
+      <c r="H5" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5">
         <v>3</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
       <c r="P5" s="2"/>
     </row>
     <row r="6" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="H6" s="3" t="s">
+      <c r="H6" t="s">
         <v>8</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6">
         <v>4</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
       <c r="P6" s="2"/>
     </row>
     <row r="7" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
       <c r="P7" s="2"/>
     </row>
     <row r="8" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
       <c r="P8" s="2"/>
     </row>
     <row r="9" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="H9" s="3" t="s">
+      <c r="H9" t="s">
         <v>10</v>
       </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
       <c r="P9" s="2"/>
     </row>
     <row r="10" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="H10" s="3" t="s">
+      <c r="H10" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" t="s">
         <v>7</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3" t="s">
+      <c r="L10" t="s">
         <v>20</v>
       </c>
-      <c r="M10" s="3"/>
       <c r="P10" s="2"/>
     </row>
     <row r="11" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="H11" s="3" t="s">
+      <c r="H11" t="s">
         <v>11</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11">
         <f>1+I5</f>
         <v>4</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11">
         <f>4+I6</f>
         <v>8</v>
       </c>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3">
+      <c r="L11">
         <f>MIN(I11:J11)</f>
         <v>4</v>
       </c>
-      <c r="M11" s="3"/>
       <c r="P11" s="2"/>
     </row>
     <row r="12" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="H12" s="3" t="s">
+      <c r="H12" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12">
         <f>6+I5</f>
         <v>9</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12">
         <f>3+I6</f>
         <v>7</v>
       </c>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3">
+      <c r="L12">
         <f t="shared" ref="L12:L13" si="0">MIN(I12:J12)</f>
         <v>7</v>
       </c>
-      <c r="M12" s="3"/>
       <c r="P12" s="2"/>
     </row>
     <row r="13" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="H13" s="3" t="s">
+      <c r="H13" t="s">
         <v>13</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13">
         <f>3+I5</f>
         <v>6</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13">
         <f>3+I6</f>
         <v>7</v>
       </c>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3">
+      <c r="L13">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="M13" s="3"/>
       <c r="P13" s="2"/>
     </row>
     <row r="14" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
       <c r="P14" s="2"/>
     </row>
     <row r="15" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="H15" s="3" t="s">
+      <c r="H15" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
     </row>
     <row r="16" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="H16" s="3" t="s">
+      <c r="H16" t="s">
         <v>14</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" t="s">
         <v>11</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="J16" t="s">
         <v>12</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="K16" t="s">
         <v>13</v>
       </c>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3" t="s">
+      <c r="M16" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H17" s="3" t="s">
+      <c r="H17" t="s">
         <v>17</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17">
         <f>7+MIN(I11:J11)</f>
         <v>11</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17">
         <f>4+MIN(I12:J12)</f>
         <v>11</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17">
         <f>6+L13</f>
         <v>12</v>
       </c>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3">
+      <c r="M17">
         <f>MIN(I17:K17)</f>
         <v>11</v>
       </c>
     </row>
     <row r="18" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H18" s="3" t="s">
+      <c r="H18" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18">
         <f>3+MIN(I11:J11)</f>
         <v>7</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18">
         <f>2+MIN(I12:J12)</f>
         <v>9</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18">
         <f>4+L13</f>
         <v>10</v>
       </c>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3">
+      <c r="M18">
         <f t="shared" ref="M18:M19" si="1">MIN(I18:K18)</f>
         <v>7</v>
       </c>
     </row>
     <row r="19" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H19" s="3" t="s">
+      <c r="H19" t="s">
         <v>19</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19">
         <f>4+MIN(I11:J11)</f>
         <v>8</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19">
         <f>1+MIN(I12:J12)</f>
         <v>8</v>
       </c>
-      <c r="K19" s="3">
+      <c r="K19">
         <f>5+L13</f>
         <v>11</v>
       </c>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3">
+      <c r="M19">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-    </row>
     <row r="21" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H21" s="3" t="s">
+      <c r="H21" t="s">
         <v>21</v>
       </c>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
     </row>
     <row r="22" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H22" s="3" t="s">
+      <c r="H22" t="s">
         <v>14</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I22" t="s">
         <v>17</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="J22" t="s">
         <v>18</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="K22" t="s">
         <v>19</v>
       </c>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3" t="s">
+      <c r="M22" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="23" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H23" s="3" t="s">
+      <c r="H23" t="s">
         <v>5</v>
       </c>
-      <c r="I23" s="3">
+      <c r="I23">
         <f>2+M17</f>
         <v>13</v>
       </c>
-      <c r="J23" s="3">
+      <c r="J23">
         <f>4+M18</f>
         <v>11</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23">
         <f>3+M19</f>
         <v>11</v>
       </c>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3">
+      <c r="M23">
         <f>MIN(I23:K23)</f>
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-    </row>
     <row r="25" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H25" s="3" t="s">
+      <c r="H25" t="s">
         <v>22</v>
       </c>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
     </row>
     <row r="26" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H26" s="3" t="s">
+      <c r="H26" t="s">
         <v>23</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="I26" t="s">
         <v>25</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
     </row>
     <row r="27" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H27" s="3" t="s">
+      <c r="H27" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I27" t="s">
         <v>26</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
     </row>
     <row r="28" spans="8:13" x14ac:dyDescent="0.35">
-      <c r="H28" s="3" t="s">
+      <c r="H28" t="s">
         <v>27</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="I28" t="s">
         <v>28</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1374,65 +1719,65 @@
   <sheetData>
     <row r="3" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="4">
+        <v>30</v>
+      </c>
+      <c r="C4" s="3">
         <v>350</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H4" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" s="18" t="s">
         <v>42</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="5" spans="2:13" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="4">
+        <v>31</v>
+      </c>
+      <c r="C5" s="3">
         <v>750</v>
       </c>
       <c r="E5" s="7">
         <v>0</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5">
         <v>400</v>
       </c>
       <c r="G5" s="8">
         <f>E5+F5-H5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H5">
         <f>$C$16</f>
         <v>400</v>
       </c>
@@ -1459,22 +1804,22 @@
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="4">
+        <v>32</v>
+      </c>
+      <c r="C6" s="3">
         <v>150000</v>
       </c>
       <c r="E6" s="7">
         <v>100</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6">
         <v>300</v>
       </c>
       <c r="G6" s="8">
         <f t="shared" ref="G6:G9" si="0">E6+F6-H6</f>
         <v>0</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6">
         <f t="shared" ref="H6:H8" si="1">$C$16</f>
         <v>400</v>
       </c>
@@ -1501,7 +1846,7 @@
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>100</v>
@@ -1509,14 +1854,14 @@
       <c r="E7" s="7">
         <v>200</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7">
         <v>200</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7">
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
@@ -1543,22 +1888,22 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="4">
+        <v>35</v>
+      </c>
+      <c r="C8" s="3">
         <v>200</v>
       </c>
       <c r="E8" s="7">
         <v>300</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8">
         <v>100</v>
       </c>
       <c r="G8" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8">
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
@@ -1585,7 +1930,7 @@
     </row>
     <row r="9" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9">
         <v>800</v>
@@ -1593,14 +1938,14 @@
       <c r="E9" s="9">
         <v>400</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="21">
         <v>0</v>
       </c>
       <c r="G9" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="21">
         <f>$C$16</f>
         <v>400</v>
       </c>
@@ -1620,33 +1965,33 @@
         <f>IF(F9&gt;0,150000,0)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="38">
+      <c r="M9" s="33">
         <f>I9-J9-K9-L9</f>
         <v>220000</v>
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.35">
       <c r="E11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
         <v>37</v>
       </c>
-      <c r="C12" t="s">
-        <v>36</v>
-      </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1656,32 +2001,32 @@
       <c r="C13">
         <v>500</v>
       </c>
-      <c r="E13" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="G13" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" s="24" t="s">
+      <c r="E13" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="L13" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="M13" s="30" t="s">
         <v>42</v>
-      </c>
-      <c r="I13" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="J13" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="K13" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="L13" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M13" s="33" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.35">
@@ -1691,37 +2036,37 @@
       <c r="C14">
         <v>600</v>
       </c>
-      <c r="E14" s="29">
-        <v>0</v>
-      </c>
-      <c r="F14" s="35">
+      <c r="E14" s="26">
+        <v>0</v>
+      </c>
+      <c r="F14" s="32">
         <v>700</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="24">
         <f>E14+F14-H14</f>
         <v>400</v>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="26">
         <f>$C$15</f>
         <v>300</v>
       </c>
-      <c r="I14" s="30">
+      <c r="I14" s="27">
         <f>H14*$C$5</f>
         <v>225000</v>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="28">
         <f>F14*350</f>
         <v>245000</v>
       </c>
-      <c r="K14" s="31">
+      <c r="K14" s="28">
         <f>E14*200</f>
         <v>0</v>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="29">
         <f>IF(F14&gt;0,150000,0)</f>
         <v>150000</v>
       </c>
-      <c r="M14" s="34">
+      <c r="M14" s="31">
         <f>I14-J14-K14-L14+MAX($M$5:$M$9)</f>
         <v>50000</v>
       </c>
@@ -1736,7 +2081,7 @@
       <c r="E15" s="7">
         <v>100</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15">
         <v>600</v>
       </c>
       <c r="G15" s="8">
@@ -1778,7 +2123,7 @@
       <c r="E16" s="7">
         <v>200</v>
       </c>
-      <c r="F16" s="21">
+      <c r="F16">
         <v>500</v>
       </c>
       <c r="G16" s="8">
@@ -1814,7 +2159,7 @@
       <c r="E17" s="7">
         <v>300</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17">
         <v>400</v>
       </c>
       <c r="G17" s="8">
@@ -1850,7 +2195,7 @@
       <c r="E18" s="7">
         <v>400</v>
       </c>
-      <c r="F18" s="21">
+      <c r="F18">
         <v>300</v>
       </c>
       <c r="G18" s="8">
@@ -1883,10 +2228,10 @@
       </c>
     </row>
     <row r="19" spans="5:13" x14ac:dyDescent="0.35">
-      <c r="E19" s="27">
+      <c r="E19" s="7">
         <v>500</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F19">
         <v>200</v>
       </c>
       <c r="G19" s="8">
@@ -1919,10 +2264,10 @@
       </c>
     </row>
     <row r="20" spans="5:13" x14ac:dyDescent="0.35">
-      <c r="E20" s="27">
+      <c r="E20" s="7">
         <v>600</v>
       </c>
-      <c r="F20" s="28">
+      <c r="F20">
         <v>100</v>
       </c>
       <c r="G20" s="8">
@@ -1955,10 +2300,10 @@
       </c>
     </row>
     <row r="21" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E21" s="36">
+      <c r="E21" s="9">
         <v>700</v>
       </c>
-      <c r="F21" s="37">
+      <c r="F21" s="21">
         <v>0</v>
       </c>
       <c r="G21" s="10">
@@ -1985,87 +2330,87 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="M21" s="38">
+      <c r="M21" s="33">
         <f t="shared" si="7"/>
         <v>305000</v>
       </c>
     </row>
     <row r="22" spans="5:13" x14ac:dyDescent="0.35">
       <c r="E22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="5:13" x14ac:dyDescent="0.35">
       <c r="E23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E25" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="F25" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="G25" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H25" s="24" t="s">
+      <c r="E25" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I25" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J25" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="K25" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="L25" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="M25" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="I25" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="J25" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="K25" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="L25" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M25" s="33" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="26" spans="5:13" x14ac:dyDescent="0.35">
-      <c r="E26" s="29">
-        <v>0</v>
-      </c>
-      <c r="F26" s="35">
+      <c r="E26" s="26">
+        <v>0</v>
+      </c>
+      <c r="F26" s="32">
         <v>900</v>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="24">
         <f>E26+F26-H26</f>
         <v>300</v>
       </c>
-      <c r="H26" s="29">
+      <c r="H26" s="26">
         <f>$C$14</f>
         <v>600</v>
       </c>
-      <c r="I26" s="30">
+      <c r="I26" s="27">
         <f>H26*$C$5</f>
         <v>450000</v>
       </c>
-      <c r="J26" s="31">
+      <c r="J26" s="28">
         <f>F26*350</f>
         <v>315000</v>
       </c>
-      <c r="K26" s="31">
+      <c r="K26" s="28">
         <f>E26*200</f>
         <v>0</v>
       </c>
-      <c r="L26" s="31">
+      <c r="L26" s="28">
         <f>IF(F26&gt;0,150000,0)</f>
         <v>150000</v>
       </c>
-      <c r="M26" s="34">
+      <c r="M26" s="31">
         <f>I26-J26-K26-L26+MAX($M$14:$M$21)</f>
         <v>290000</v>
       </c>
@@ -2074,7 +2419,7 @@
       <c r="E27" s="7">
         <v>100</v>
       </c>
-      <c r="F27" s="21">
+      <c r="F27">
         <v>800</v>
       </c>
       <c r="G27" s="8">
@@ -2110,7 +2455,7 @@
       <c r="E28" s="7">
         <v>200</v>
       </c>
-      <c r="F28" s="21">
+      <c r="F28">
         <v>700</v>
       </c>
       <c r="G28" s="8">
@@ -2146,7 +2491,7 @@
       <c r="E29" s="7">
         <v>300</v>
       </c>
-      <c r="F29" s="21">
+      <c r="F29">
         <v>600</v>
       </c>
       <c r="G29" s="8">
@@ -2182,7 +2527,7 @@
       <c r="E30" s="7">
         <v>400</v>
       </c>
-      <c r="F30" s="21">
+      <c r="F30">
         <v>500</v>
       </c>
       <c r="G30" s="8">
@@ -2215,10 +2560,10 @@
       </c>
     </row>
     <row r="31" spans="5:13" x14ac:dyDescent="0.35">
-      <c r="E31" s="27">
+      <c r="E31" s="7">
         <v>500</v>
       </c>
-      <c r="F31" s="28">
+      <c r="F31">
         <v>400</v>
       </c>
       <c r="G31" s="8">
@@ -2251,10 +2596,10 @@
       </c>
     </row>
     <row r="32" spans="5:13" x14ac:dyDescent="0.35">
-      <c r="E32" s="27">
+      <c r="E32" s="7">
         <v>600</v>
       </c>
-      <c r="F32" s="28">
+      <c r="F32">
         <v>300</v>
       </c>
       <c r="G32" s="8">
@@ -2287,10 +2632,10 @@
       </c>
     </row>
     <row r="33" spans="5:13" x14ac:dyDescent="0.35">
-      <c r="E33" s="27">
+      <c r="E33" s="7">
         <v>700</v>
       </c>
-      <c r="F33" s="28">
+      <c r="F33">
         <v>200</v>
       </c>
       <c r="G33" s="8">
@@ -2323,10 +2668,10 @@
       </c>
     </row>
     <row r="34" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E34" s="36">
+      <c r="E34" s="9">
         <v>800</v>
       </c>
-      <c r="F34" s="37">
+      <c r="F34" s="21">
         <v>100</v>
       </c>
       <c r="G34" s="10">
@@ -2360,70 +2705,70 @@
     </row>
     <row r="37" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="E37" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E38" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="F38" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="G38" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="H38" s="24" t="s">
+      <c r="E38" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="G38" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="H38" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="I38" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J38" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="K38" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="L38" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="M38" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="I38" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="J38" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="K38" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="L38" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M38" s="33" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="39" spans="5:13" x14ac:dyDescent="0.35">
-      <c r="E39" s="29">
-        <v>0</v>
-      </c>
-      <c r="F39" s="35">
+      <c r="E39" s="26">
+        <v>0</v>
+      </c>
+      <c r="F39" s="32">
         <v>900</v>
       </c>
-      <c r="G39" s="25">
+      <c r="G39" s="24">
         <f>E39+F39-H39</f>
         <v>400</v>
       </c>
-      <c r="H39" s="29">
+      <c r="H39" s="26">
         <f>$C$13</f>
         <v>500</v>
       </c>
-      <c r="I39" s="30">
+      <c r="I39" s="27">
         <f>H39*$C$5</f>
         <v>375000</v>
       </c>
-      <c r="J39" s="31">
+      <c r="J39" s="28">
         <f>F39*350</f>
         <v>315000</v>
       </c>
-      <c r="K39" s="31">
+      <c r="K39" s="28">
         <f>E39*200</f>
         <v>0</v>
       </c>
-      <c r="L39" s="31">
+      <c r="L39" s="28">
         <f>IF(F39&gt;0,150000,0)</f>
         <v>150000</v>
       </c>
-      <c r="M39" s="34">
+      <c r="M39" s="31">
         <f>I39-J39-K39-L39+MAX($M$14:$M$21)</f>
         <v>215000</v>
       </c>
@@ -2432,7 +2777,7 @@
       <c r="E40" s="7">
         <v>0</v>
       </c>
-      <c r="F40" s="21">
+      <c r="F40">
         <v>800</v>
       </c>
       <c r="G40" s="8">
@@ -2468,7 +2813,7 @@
       <c r="E41" s="7">
         <v>0</v>
       </c>
-      <c r="F41" s="21">
+      <c r="F41">
         <v>700</v>
       </c>
       <c r="G41" s="8">
@@ -2504,7 +2849,7 @@
       <c r="E42" s="7">
         <v>0</v>
       </c>
-      <c r="F42" s="21">
+      <c r="F42">
         <v>600</v>
       </c>
       <c r="G42" s="8">
@@ -2540,7 +2885,7 @@
       <c r="E43" s="7">
         <v>0</v>
       </c>
-      <c r="F43" s="21">
+      <c r="F43">
         <v>500</v>
       </c>
       <c r="G43" s="8">
@@ -2573,10 +2918,10 @@
       </c>
     </row>
     <row r="44" spans="5:13" x14ac:dyDescent="0.35">
-      <c r="E44" s="27">
-        <v>0</v>
-      </c>
-      <c r="F44" s="28">
+      <c r="E44" s="7">
+        <v>0</v>
+      </c>
+      <c r="F44">
         <v>400</v>
       </c>
       <c r="G44" s="8">
@@ -2609,10 +2954,10 @@
       </c>
     </row>
     <row r="45" spans="5:13" x14ac:dyDescent="0.35">
-      <c r="E45" s="27">
-        <v>0</v>
-      </c>
-      <c r="F45" s="28">
+      <c r="E45" s="7">
+        <v>0</v>
+      </c>
+      <c r="F45">
         <v>300</v>
       </c>
       <c r="G45" s="8">
@@ -2645,10 +2990,10 @@
       </c>
     </row>
     <row r="46" spans="5:13" x14ac:dyDescent="0.35">
-      <c r="E46" s="27">
-        <v>0</v>
-      </c>
-      <c r="F46" s="28">
+      <c r="E46" s="7">
+        <v>0</v>
+      </c>
+      <c r="F46">
         <v>200</v>
       </c>
       <c r="G46" s="8">
@@ -2681,10 +3026,10 @@
       </c>
     </row>
     <row r="47" spans="5:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="E47" s="36">
-        <v>0</v>
-      </c>
-      <c r="F47" s="37">
+      <c r="E47" s="9">
+        <v>0</v>
+      </c>
+      <c r="F47" s="21">
         <v>100</v>
       </c>
       <c r="G47" s="10">
@@ -2719,4 +3064,7993 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62241E21-291C-4798-9C4C-DE66E3492F76}">
+  <dimension ref="M4:U85"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="13" max="13" width="25.26953125" customWidth="1"/>
+    <col min="14" max="14" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M5" t="s">
+        <v>58</v>
+      </c>
+      <c r="N5">
+        <v>5</v>
+      </c>
+      <c r="O5" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N6">
+        <v>250</v>
+      </c>
+      <c r="O6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q6">
+        <v>2</v>
+      </c>
+      <c r="R6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M7" t="s">
+        <v>44</v>
+      </c>
+      <c r="N7">
+        <v>150</v>
+      </c>
+      <c r="O7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q7">
+        <v>3</v>
+      </c>
+      <c r="R7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M8" t="s">
+        <v>62</v>
+      </c>
+      <c r="N8">
+        <v>3</v>
+      </c>
+      <c r="O8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M9" t="s">
+        <v>63</v>
+      </c>
+      <c r="N9">
+        <v>100</v>
+      </c>
+      <c r="O9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M10" t="s">
+        <v>64</v>
+      </c>
+      <c r="N10">
+        <v>50</v>
+      </c>
+      <c r="O10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M11" t="s">
+        <v>65</v>
+      </c>
+      <c r="N11">
+        <v>2</v>
+      </c>
+      <c r="O11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="15" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M15" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
+      <c r="T15" s="32"/>
+      <c r="U15" s="24"/>
+    </row>
+    <row r="16" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M16" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="U16" s="8"/>
+    </row>
+    <row r="17" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M17" s="7"/>
+      <c r="U17" s="8"/>
+    </row>
+    <row r="18" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M18" s="7"/>
+      <c r="U18" s="8"/>
+    </row>
+    <row r="19" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M19" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" t="s">
+        <v>66</v>
+      </c>
+      <c r="O19" t="s">
+        <v>69</v>
+      </c>
+      <c r="P19" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>70</v>
+      </c>
+      <c r="R19" t="s">
+        <v>71</v>
+      </c>
+      <c r="S19" t="s">
+        <v>64</v>
+      </c>
+      <c r="T19" t="s">
+        <v>63</v>
+      </c>
+      <c r="U19" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M20" s="7">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <f>$R$7</f>
+        <v>4</v>
+      </c>
+      <c r="O20">
+        <f>N20-M20</f>
+        <v>4</v>
+      </c>
+      <c r="P20">
+        <f>M20+O20-N20</f>
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <f>O20*$N$7</f>
+        <v>600</v>
+      </c>
+      <c r="R20">
+        <f>$N$6*IF(O20&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S20">
+        <f>$N$10*M20</f>
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <f>$N$9*IF(M20&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U20" s="36">
+        <f>SUM(Q20:T20)</f>
+        <v>850</v>
+      </c>
+    </row>
+    <row r="21" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M21" s="7">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <f t="shared" ref="N21:N23" si="0">$R$7</f>
+        <v>4</v>
+      </c>
+      <c r="O21">
+        <f t="shared" ref="O21:O23" si="1">N21-M21</f>
+        <v>3</v>
+      </c>
+      <c r="P21">
+        <f t="shared" ref="P21:P23" si="2">M21+O21-N21</f>
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <f>O21*$N$7</f>
+        <v>450</v>
+      </c>
+      <c r="R21">
+        <f>$N$6*IF(O21&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S21">
+        <f>$N$10*M21</f>
+        <v>50</v>
+      </c>
+      <c r="T21">
+        <f>$N$9*IF(M21&gt;0,1,0)</f>
+        <v>100</v>
+      </c>
+      <c r="U21" s="8">
+        <f t="shared" ref="U21:U23" si="3">SUM(Q21:T21)</f>
+        <v>850</v>
+      </c>
+    </row>
+    <row r="22" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M22" s="7">
+        <v>2</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <f>O22*$N$7</f>
+        <v>300</v>
+      </c>
+      <c r="R22">
+        <f>$N$6*IF(O22&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S22">
+        <f>$N$10*M22</f>
+        <v>100</v>
+      </c>
+      <c r="T22">
+        <f>$N$9*IF(M22&gt;0,1,0)</f>
+        <v>100</v>
+      </c>
+      <c r="U22" s="8">
+        <f t="shared" si="3"/>
+        <v>750</v>
+      </c>
+    </row>
+    <row r="23" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M23" s="9">
+        <v>3</v>
+      </c>
+      <c r="N23" s="21">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="O23" s="21">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P23" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="21">
+        <f>O23*$N$7</f>
+        <v>150</v>
+      </c>
+      <c r="R23" s="21">
+        <f>$N$6*IF(O23&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S23" s="21">
+        <f>$N$10*M23</f>
+        <v>150</v>
+      </c>
+      <c r="T23" s="21">
+        <f>$N$9*IF(M23&gt;0,1,0)</f>
+        <v>100</v>
+      </c>
+      <c r="U23" s="10">
+        <f t="shared" si="3"/>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="25" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="26" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M26" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="N26" s="32"/>
+      <c r="O26" s="32"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="24"/>
+    </row>
+    <row r="27" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M27" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="U27" s="8"/>
+    </row>
+    <row r="28" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M28" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="U28" s="8"/>
+    </row>
+    <row r="29" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M29" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" t="s">
+        <v>66</v>
+      </c>
+      <c r="O29" t="s">
+        <v>69</v>
+      </c>
+      <c r="P29" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>70</v>
+      </c>
+      <c r="R29" t="s">
+        <v>71</v>
+      </c>
+      <c r="S29" t="s">
+        <v>64</v>
+      </c>
+      <c r="T29" t="s">
+        <v>63</v>
+      </c>
+      <c r="U29" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M30" s="7">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <f>$R$6</f>
+        <v>2</v>
+      </c>
+      <c r="O30">
+        <f>N30-M30</f>
+        <v>2</v>
+      </c>
+      <c r="P30">
+        <f>M30+O30-N30</f>
+        <v>0</v>
+      </c>
+      <c r="Q30">
+        <f>O30*$N$7</f>
+        <v>300</v>
+      </c>
+      <c r="R30">
+        <f>$N$6*IF(O30&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S30">
+        <f>$N$10*M30</f>
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <f>$N$9*IF(M30&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U30" s="8">
+        <f>SUM(Q30:T30)+$U$20</f>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="31" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M31" s="7">
+        <v>1</v>
+      </c>
+      <c r="N31">
+        <f t="shared" ref="N31:N32" si="4">$R$6</f>
+        <v>2</v>
+      </c>
+      <c r="O31">
+        <f t="shared" ref="O31:O32" si="5">N31-M31</f>
+        <v>1</v>
+      </c>
+      <c r="P31">
+        <f t="shared" ref="P31:P32" si="6">M31+O31-N31</f>
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <f>O31*$N$7</f>
+        <v>150</v>
+      </c>
+      <c r="R31">
+        <f>$N$6*IF(O31&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S31">
+        <f>$N$10*M31</f>
+        <v>50</v>
+      </c>
+      <c r="T31">
+        <f>$N$9*IF(M31&gt;0,1,0)</f>
+        <v>100</v>
+      </c>
+      <c r="U31" s="8">
+        <f>SUM(Q31:T31)+$U$20</f>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="32" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M32" s="7">
+        <v>2</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="O32">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q32">
+        <f>O32*$N$7</f>
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <f>$N$6*IF(O32&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <f>$N$10*M32</f>
+        <v>100</v>
+      </c>
+      <c r="T32">
+        <f>$N$9*IF(M32&gt;0,1,0)</f>
+        <v>100</v>
+      </c>
+      <c r="U32" s="36">
+        <f>SUM(Q32:T32)+$U$20</f>
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="33" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M33" s="7"/>
+      <c r="U33" s="8"/>
+    </row>
+    <row r="34" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M34" s="7"/>
+      <c r="U34" s="8"/>
+    </row>
+    <row r="35" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M35" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="U35" s="8"/>
+    </row>
+    <row r="36" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M36" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N36">
+        <v>1</v>
+      </c>
+      <c r="U36" s="8"/>
+    </row>
+    <row r="37" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M37" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" t="s">
+        <v>66</v>
+      </c>
+      <c r="O37" t="s">
+        <v>69</v>
+      </c>
+      <c r="P37" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>70</v>
+      </c>
+      <c r="R37" t="s">
+        <v>71</v>
+      </c>
+      <c r="S37" t="s">
+        <v>64</v>
+      </c>
+      <c r="T37" t="s">
+        <v>63</v>
+      </c>
+      <c r="U37" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M38" s="7">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <f>$R$6</f>
+        <v>2</v>
+      </c>
+      <c r="O38">
+        <v>3</v>
+      </c>
+      <c r="P38">
+        <f>M38+O38-N38</f>
+        <v>1</v>
+      </c>
+      <c r="Q38">
+        <f>O38*$N$7</f>
+        <v>450</v>
+      </c>
+      <c r="R38">
+        <f>$N$6*IF(O38&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S38">
+        <f>$N$10*M38</f>
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <f>$N$9*IF(M38&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U38" s="8">
+        <f>SUM(Q38:T38)+$U$21</f>
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="39" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M39" s="7">
+        <v>1</v>
+      </c>
+      <c r="N39">
+        <f t="shared" ref="N39:N41" si="7">$R$6</f>
+        <v>2</v>
+      </c>
+      <c r="O39">
+        <v>2</v>
+      </c>
+      <c r="P39">
+        <f t="shared" ref="P39:P41" si="8">M39+O39-N39</f>
+        <v>1</v>
+      </c>
+      <c r="Q39">
+        <f>O39*$N$7</f>
+        <v>300</v>
+      </c>
+      <c r="R39">
+        <f>$N$6*IF(O39&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S39">
+        <f>$N$10*M39</f>
+        <v>50</v>
+      </c>
+      <c r="T39">
+        <f>$N$9*IF(M39&gt;0,1,0)</f>
+        <v>100</v>
+      </c>
+      <c r="U39" s="8">
+        <f>SUM(Q39:T39)+$U$21</f>
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="40" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M40" s="7">
+        <v>2</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="O40">
+        <v>1</v>
+      </c>
+      <c r="P40">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="Q40">
+        <f>O40*$N$7</f>
+        <v>150</v>
+      </c>
+      <c r="R40">
+        <f>$N$6*IF(O40&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S40">
+        <f>$N$10*M40</f>
+        <v>100</v>
+      </c>
+      <c r="T40">
+        <f>$N$9*IF(M40&gt;0,1,0)</f>
+        <v>100</v>
+      </c>
+      <c r="U40" s="8">
+        <f>SUM(Q40:T40)+$U$21</f>
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="41" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M41" s="7">
+        <v>3</v>
+      </c>
+      <c r="N41">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="Q41">
+        <f>O41*$N$7</f>
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <f>$N$6*IF(O41&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <f>$N$10*M41</f>
+        <v>150</v>
+      </c>
+      <c r="T41">
+        <f>$N$9*IF(M41&gt;0,1,0)</f>
+        <v>100</v>
+      </c>
+      <c r="U41" s="8">
+        <f>SUM(Q41:T41)+$U$21</f>
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="42" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M42" s="7"/>
+      <c r="U42" s="8"/>
+    </row>
+    <row r="43" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M43" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="U43" s="8"/>
+    </row>
+    <row r="44" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M44" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N44">
+        <v>2</v>
+      </c>
+      <c r="U44" s="8"/>
+    </row>
+    <row r="45" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M45" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" t="s">
+        <v>66</v>
+      </c>
+      <c r="O45" t="s">
+        <v>69</v>
+      </c>
+      <c r="P45" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>70</v>
+      </c>
+      <c r="R45" t="s">
+        <v>71</v>
+      </c>
+      <c r="S45" t="s">
+        <v>64</v>
+      </c>
+      <c r="T45" t="s">
+        <v>63</v>
+      </c>
+      <c r="U45" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M46" s="7">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <f>$R$6</f>
+        <v>2</v>
+      </c>
+      <c r="O46">
+        <v>4</v>
+      </c>
+      <c r="P46">
+        <f>M46+O46-N46</f>
+        <v>2</v>
+      </c>
+      <c r="Q46">
+        <f>O46*$N$7</f>
+        <v>600</v>
+      </c>
+      <c r="R46">
+        <f>$N$6*IF(O46&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S46">
+        <f>$N$10*M46</f>
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <f>$N$9*IF(M46&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U46" s="8">
+        <f>SUM(Q46:T46)+$U$22</f>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="47" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M47" s="7">
+        <v>1</v>
+      </c>
+      <c r="N47">
+        <f t="shared" ref="N47:N49" si="9">$R$6</f>
+        <v>2</v>
+      </c>
+      <c r="O47">
+        <v>3</v>
+      </c>
+      <c r="P47">
+        <f t="shared" ref="P47:P49" si="10">M47+O47-N47</f>
+        <v>2</v>
+      </c>
+      <c r="Q47">
+        <f>O47*$N$7</f>
+        <v>450</v>
+      </c>
+      <c r="R47">
+        <f>$N$6*IF(O47&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S47">
+        <f>$N$10*M47</f>
+        <v>50</v>
+      </c>
+      <c r="T47">
+        <f>$N$9*IF(M47&gt;0,1,0)</f>
+        <v>100</v>
+      </c>
+      <c r="U47" s="8">
+        <f>SUM(Q47:T47)+$U$22</f>
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="48" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M48" s="7">
+        <v>2</v>
+      </c>
+      <c r="N48">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="O48">
+        <v>2</v>
+      </c>
+      <c r="P48">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="Q48">
+        <f>O48*$N$7</f>
+        <v>300</v>
+      </c>
+      <c r="R48">
+        <f>$N$6*IF(O48&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S48">
+        <f>$N$10*M48</f>
+        <v>100</v>
+      </c>
+      <c r="T48">
+        <f>$N$9*IF(M48&gt;0,1,0)</f>
+        <v>100</v>
+      </c>
+      <c r="U48" s="8">
+        <f>SUM(Q48:T48)+$U$22</f>
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="49" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M49" s="7">
+        <v>3</v>
+      </c>
+      <c r="N49">
+        <f t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="O49">
+        <v>1</v>
+      </c>
+      <c r="P49">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="Q49">
+        <f>O49*$N$7</f>
+        <v>150</v>
+      </c>
+      <c r="R49">
+        <f>$N$6*IF(O49&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S49">
+        <f>$N$10*M49</f>
+        <v>150</v>
+      </c>
+      <c r="T49">
+        <f>$N$9*IF(M49&gt;0,1,0)</f>
+        <v>100</v>
+      </c>
+      <c r="U49" s="8">
+        <f>SUM(Q49:T49)+$U$22</f>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="50" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M50" s="7"/>
+      <c r="U50" s="8"/>
+    </row>
+    <row r="51" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M51" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="U51" s="8"/>
+    </row>
+    <row r="52" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M52" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N52">
+        <v>3</v>
+      </c>
+      <c r="U52" s="8"/>
+    </row>
+    <row r="53" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M53" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="N53" t="s">
+        <v>66</v>
+      </c>
+      <c r="O53" t="s">
+        <v>69</v>
+      </c>
+      <c r="P53" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>70</v>
+      </c>
+      <c r="R53" t="s">
+        <v>71</v>
+      </c>
+      <c r="S53" t="s">
+        <v>64</v>
+      </c>
+      <c r="T53" t="s">
+        <v>63</v>
+      </c>
+      <c r="U53" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="54" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M54" s="7">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <f>$R$6</f>
+        <v>2</v>
+      </c>
+      <c r="O54">
+        <v>5</v>
+      </c>
+      <c r="P54">
+        <f>M54+O54-N54</f>
+        <v>3</v>
+      </c>
+      <c r="Q54">
+        <f>O54*$N$7</f>
+        <v>750</v>
+      </c>
+      <c r="R54">
+        <f>$N$6*IF(O54&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S54">
+        <f>$N$10*M54</f>
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <f>$N$9*IF(M54&gt;0,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U54" s="8">
+        <f>SUM(Q54:T54)+$U$23</f>
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="55" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M55" s="7">
+        <v>1</v>
+      </c>
+      <c r="N55">
+        <f t="shared" ref="N55:N57" si="11">$R$6</f>
+        <v>2</v>
+      </c>
+      <c r="O55">
+        <v>4</v>
+      </c>
+      <c r="P55">
+        <f t="shared" ref="P55:P57" si="12">M55+O55-N55</f>
+        <v>3</v>
+      </c>
+      <c r="Q55">
+        <f>O55*$N$7</f>
+        <v>600</v>
+      </c>
+      <c r="R55">
+        <f>$N$6*IF(O55&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S55">
+        <f>$N$10*M55</f>
+        <v>50</v>
+      </c>
+      <c r="T55">
+        <f>$N$9*IF(M55&gt;0,1,0)</f>
+        <v>100</v>
+      </c>
+      <c r="U55" s="8">
+        <f>SUM(Q55:T55)+$U$23</f>
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="56" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M56" s="7">
+        <v>2</v>
+      </c>
+      <c r="N56">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="O56">
+        <v>3</v>
+      </c>
+      <c r="P56">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="Q56">
+        <f>O56*$N$7</f>
+        <v>450</v>
+      </c>
+      <c r="R56">
+        <f>$N$6*IF(O56&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S56">
+        <f>$N$10*M56</f>
+        <v>100</v>
+      </c>
+      <c r="T56">
+        <f>$N$9*IF(M56&gt;0,1,0)</f>
+        <v>100</v>
+      </c>
+      <c r="U56" s="8">
+        <f>SUM(Q56:T56)+$U$23</f>
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="57" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M57" s="7">
+        <v>3</v>
+      </c>
+      <c r="N57">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="O57">
+        <v>2</v>
+      </c>
+      <c r="P57">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="Q57">
+        <f>O57*$N$7</f>
+        <v>300</v>
+      </c>
+      <c r="R57">
+        <f>$N$6*IF(O57&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S57">
+        <f>$N$10*M57</f>
+        <v>150</v>
+      </c>
+      <c r="T57">
+        <f>$N$9*IF(M57&gt;0,1,0)</f>
+        <v>100</v>
+      </c>
+      <c r="U57" s="8">
+        <f>SUM(Q57:T57)+$U$23</f>
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="58" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M58" s="7"/>
+      <c r="U58" s="8"/>
+    </row>
+    <row r="59" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M59" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="N59" t="s">
+        <v>77</v>
+      </c>
+      <c r="U59" s="8"/>
+    </row>
+    <row r="60" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M60" s="7">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <f>MIN(U30,U38,U46,U54)</f>
+        <v>1400</v>
+      </c>
+      <c r="U60" s="8"/>
+    </row>
+    <row r="61" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M61" s="7">
+        <v>1</v>
+      </c>
+      <c r="N61">
+        <f t="shared" ref="N61:N63" si="13">MIN(U31,U39,U47,U55)</f>
+        <v>1400</v>
+      </c>
+      <c r="U61" s="8"/>
+    </row>
+    <row r="62" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M62" s="7">
+        <v>2</v>
+      </c>
+      <c r="N62" s="35">
+        <f t="shared" si="13"/>
+        <v>1050</v>
+      </c>
+      <c r="U62" s="8"/>
+    </row>
+    <row r="63" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M63" s="9">
+        <v>3</v>
+      </c>
+      <c r="N63" s="21">
+        <f t="shared" si="13"/>
+        <v>1100</v>
+      </c>
+      <c r="O63" s="21"/>
+      <c r="P63" s="21"/>
+      <c r="Q63" s="21"/>
+      <c r="R63" s="21"/>
+      <c r="S63" s="21"/>
+      <c r="T63" s="21"/>
+      <c r="U63" s="10"/>
+    </row>
+    <row r="64" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="65" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M65" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="N65" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="O65" s="32">
+        <v>2</v>
+      </c>
+      <c r="P65" s="32"/>
+      <c r="Q65" s="32"/>
+      <c r="R65" s="32"/>
+      <c r="S65" s="32"/>
+      <c r="T65" s="32"/>
+      <c r="U65" s="24"/>
+    </row>
+    <row r="66" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M66" s="7"/>
+      <c r="U66" s="8"/>
+    </row>
+    <row r="67" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M67" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="U67" s="8"/>
+    </row>
+    <row r="68" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M68" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N68">
+        <v>0</v>
+      </c>
+      <c r="U68" s="8"/>
+    </row>
+    <row r="69" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M69" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="N69" t="s">
+        <v>66</v>
+      </c>
+      <c r="O69" t="s">
+        <v>69</v>
+      </c>
+      <c r="P69" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>70</v>
+      </c>
+      <c r="R69" t="s">
+        <v>71</v>
+      </c>
+      <c r="S69" t="s">
+        <v>64</v>
+      </c>
+      <c r="T69" t="s">
+        <v>63</v>
+      </c>
+      <c r="U69" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="70" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M70" s="7">
+        <f>$O$65</f>
+        <v>2</v>
+      </c>
+      <c r="N70">
+        <f>$R$5</f>
+        <v>5</v>
+      </c>
+      <c r="O70">
+        <v>3</v>
+      </c>
+      <c r="P70">
+        <f>M70+O70-N70</f>
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <f>O70*$N$7</f>
+        <v>450</v>
+      </c>
+      <c r="R70">
+        <f>$N$6*IF(O70&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S70">
+        <f>$N$10*M70</f>
+        <v>100</v>
+      </c>
+      <c r="T70">
+        <f>$N$9*IF(M70&gt;0,1,0)</f>
+        <v>100</v>
+      </c>
+      <c r="U70" s="8">
+        <f>SUM(Q70:T70)+N60</f>
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="71" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M71" s="7"/>
+      <c r="U71" s="8"/>
+    </row>
+    <row r="72" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M72" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="U72" s="8"/>
+    </row>
+    <row r="73" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M73" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N73">
+        <v>1</v>
+      </c>
+      <c r="U73" s="8"/>
+    </row>
+    <row r="74" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M74" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="N74" t="s">
+        <v>66</v>
+      </c>
+      <c r="O74" t="s">
+        <v>69</v>
+      </c>
+      <c r="P74" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>70</v>
+      </c>
+      <c r="R74" t="s">
+        <v>71</v>
+      </c>
+      <c r="S74" t="s">
+        <v>64</v>
+      </c>
+      <c r="T74" t="s">
+        <v>63</v>
+      </c>
+      <c r="U74" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="75" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M75" s="7">
+        <f>$O$65</f>
+        <v>2</v>
+      </c>
+      <c r="N75">
+        <f>$R$5</f>
+        <v>5</v>
+      </c>
+      <c r="O75">
+        <v>4</v>
+      </c>
+      <c r="P75">
+        <f>M75+O75-N75</f>
+        <v>1</v>
+      </c>
+      <c r="Q75">
+        <f>O75*$N$7</f>
+        <v>600</v>
+      </c>
+      <c r="R75">
+        <f>$N$6*IF(O75&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S75">
+        <f>$N$10*M75</f>
+        <v>100</v>
+      </c>
+      <c r="T75">
+        <f>$N$9*IF(M75&gt;0,1,0)</f>
+        <v>100</v>
+      </c>
+      <c r="U75" s="8">
+        <f>SUM(Q75:T75)+N61</f>
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="76" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M76" s="7"/>
+      <c r="U76" s="8"/>
+    </row>
+    <row r="77" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M77" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="U77" s="8"/>
+    </row>
+    <row r="78" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M78" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N78">
+        <v>2</v>
+      </c>
+      <c r="U78" s="8"/>
+    </row>
+    <row r="79" spans="13:21" x14ac:dyDescent="0.35">
+      <c r="M79" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="N79" t="s">
+        <v>66</v>
+      </c>
+      <c r="O79" t="s">
+        <v>69</v>
+      </c>
+      <c r="P79" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>70</v>
+      </c>
+      <c r="R79" t="s">
+        <v>71</v>
+      </c>
+      <c r="S79" t="s">
+        <v>64</v>
+      </c>
+      <c r="T79" t="s">
+        <v>63</v>
+      </c>
+      <c r="U79" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="80" spans="13:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M80" s="9">
+        <f>$O$65</f>
+        <v>2</v>
+      </c>
+      <c r="N80" s="21">
+        <f>$R$5</f>
+        <v>5</v>
+      </c>
+      <c r="O80" s="21">
+        <v>5</v>
+      </c>
+      <c r="P80" s="21">
+        <f>M80+O80-N80</f>
+        <v>2</v>
+      </c>
+      <c r="Q80" s="21">
+        <f>O80*$N$7</f>
+        <v>750</v>
+      </c>
+      <c r="R80" s="21">
+        <f>$N$6*IF(O80&gt;0,1,0)</f>
+        <v>250</v>
+      </c>
+      <c r="S80" s="21">
+        <f>$N$10*M80</f>
+        <v>100</v>
+      </c>
+      <c r="T80" s="21">
+        <f>$N$9*IF(M80&gt;0,1,0)</f>
+        <v>100</v>
+      </c>
+      <c r="U80" s="34">
+        <f>SUM(Q80:T80)+N62</f>
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="81" spans="13:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="82" spans="13:14" x14ac:dyDescent="0.35">
+      <c r="M82" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="N82" s="24"/>
+    </row>
+    <row r="83" spans="13:14" x14ac:dyDescent="0.35">
+      <c r="M83" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="N83" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="13:14" x14ac:dyDescent="0.35">
+      <c r="M84" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N84" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="13:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="M85" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="N85" s="10">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AEA9533-4D6E-468E-AD22-2DD0482FFBDD}">
+  <dimension ref="C3:P198"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="23.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="32.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.1796875" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="24.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D3" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" t="s">
+        <v>88</v>
+      </c>
+      <c r="I4" t="s">
+        <v>94</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>20</v>
+      </c>
+      <c r="L4" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5">
+        <v>10</v>
+      </c>
+      <c r="L5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6">
+        <v>400</v>
+      </c>
+      <c r="F6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I6" t="s">
+        <v>96</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>50</v>
+      </c>
+      <c r="L6" s="4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7">
+        <v>70</v>
+      </c>
+      <c r="F7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" t="s">
+        <v>89</v>
+      </c>
+      <c r="I7" t="s">
+        <v>97</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+      <c r="L7" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
+      </c>
+      <c r="F8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" t="s">
+        <v>88</v>
+      </c>
+      <c r="I8" t="s">
+        <v>98</v>
+      </c>
+      <c r="J8">
+        <v>5</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" t="s">
+        <v>89</v>
+      </c>
+      <c r="L9" s="4"/>
+    </row>
+    <row r="13" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="14" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D14" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="24"/>
+    </row>
+    <row r="15" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D15" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="38">
+        <v>0</v>
+      </c>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="8"/>
+    </row>
+    <row r="16" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D16" s="7"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="P16" s="24" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D17" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M17" s="38"/>
+      <c r="N17" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="O17" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="P17" s="43" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="18" spans="4:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="D18" s="7">
+        <v>0</v>
+      </c>
+      <c r="E18" s="38">
+        <f>$K$8</f>
+        <v>20</v>
+      </c>
+      <c r="F18" s="60">
+        <f>E18+G18-D18</f>
+        <v>20</v>
+      </c>
+      <c r="G18" s="60">
+        <v>0</v>
+      </c>
+      <c r="H18" s="86">
+        <f>$E$7*F18</f>
+        <v>1400</v>
+      </c>
+      <c r="I18" s="60">
+        <f>$E$6*IF(F18&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J18" s="60">
+        <f>D18*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="60">
+        <v>0</v>
+      </c>
+      <c r="L18" s="85">
+        <f>SUM(H18:K18)</f>
+        <v>1800</v>
+      </c>
+      <c r="M18" s="38"/>
+      <c r="N18" s="7">
+        <f>IF(F18&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O18" s="38">
+        <f>IF(G18&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P18" s="8">
+        <f>IF(D18&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D19" s="7">
+        <v>5</v>
+      </c>
+      <c r="E19" s="38">
+        <f t="shared" ref="E19:E22" si="0">$K$8</f>
+        <v>20</v>
+      </c>
+      <c r="F19" s="38">
+        <f t="shared" ref="F19:F22" si="1">E19+G19-D19</f>
+        <v>15</v>
+      </c>
+      <c r="G19" s="38">
+        <v>0</v>
+      </c>
+      <c r="H19" s="37">
+        <f t="shared" ref="H19:H22" si="2">$E$7*F19</f>
+        <v>1050</v>
+      </c>
+      <c r="I19" s="38">
+        <f t="shared" ref="I19:I22" si="3">$E$6*IF(F19&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J19" s="38">
+        <f t="shared" ref="J19:J22" si="4">D19*$E$9</f>
+        <v>50</v>
+      </c>
+      <c r="K19" s="38">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8">
+        <f>SUM(H19:K19)</f>
+        <v>1500</v>
+      </c>
+      <c r="M19" s="38"/>
+      <c r="N19" s="7">
+        <f t="shared" ref="N19:N22" si="5">IF(F19&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O19" s="38">
+        <f t="shared" ref="O19:O22" si="6">IF(G19&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P19" s="8">
+        <f>IF(D19&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D20" s="7">
+        <v>10</v>
+      </c>
+      <c r="E20" s="38">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F20" s="38">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="G20" s="38">
+        <v>0</v>
+      </c>
+      <c r="H20" s="37">
+        <f t="shared" si="2"/>
+        <v>700</v>
+      </c>
+      <c r="I20" s="38">
+        <f t="shared" si="3"/>
+        <v>400</v>
+      </c>
+      <c r="J20" s="38">
+        <f t="shared" si="4"/>
+        <v>100</v>
+      </c>
+      <c r="K20" s="38">
+        <v>0</v>
+      </c>
+      <c r="L20" s="8">
+        <f t="shared" ref="L20:L22" si="7">SUM(H20:K20)</f>
+        <v>1200</v>
+      </c>
+      <c r="M20" s="38"/>
+      <c r="N20" s="7">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O20" s="38">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="P20" s="8">
+        <f>IF(D20&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D21" s="7">
+        <v>15</v>
+      </c>
+      <c r="E21" s="38">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F21" s="38">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="G21" s="38">
+        <v>0</v>
+      </c>
+      <c r="H21" s="37">
+        <f t="shared" si="2"/>
+        <v>350</v>
+      </c>
+      <c r="I21" s="38">
+        <f t="shared" si="3"/>
+        <v>400</v>
+      </c>
+      <c r="J21" s="38">
+        <f t="shared" si="4"/>
+        <v>150</v>
+      </c>
+      <c r="K21" s="38">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8">
+        <f t="shared" si="7"/>
+        <v>900</v>
+      </c>
+      <c r="M21" s="38"/>
+      <c r="N21" s="7">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O21" s="38">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="P21" s="8">
+        <f>IF(D21&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D22" s="9">
+        <v>20</v>
+      </c>
+      <c r="E22" s="21">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="F22" s="87">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="21">
+        <v>0</v>
+      </c>
+      <c r="H22" s="39">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="21">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="21">
+        <f t="shared" si="4"/>
+        <v>200</v>
+      </c>
+      <c r="K22" s="21">
+        <v>0</v>
+      </c>
+      <c r="L22" s="73">
+        <f t="shared" si="7"/>
+        <v>200</v>
+      </c>
+      <c r="M22" s="21"/>
+      <c r="N22" s="9">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O22" s="21">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="P22" s="10">
+        <f>IF(D22&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="25" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D25" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="32"/>
+      <c r="P25" s="24"/>
+    </row>
+    <row r="26" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D26" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="38"/>
+      <c r="P26" s="8"/>
+    </row>
+    <row r="27" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D27" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" s="38">
+        <v>0</v>
+      </c>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="38"/>
+      <c r="J27" s="38"/>
+      <c r="K27" s="38"/>
+      <c r="L27" s="38"/>
+      <c r="M27" s="38"/>
+      <c r="N27" s="38"/>
+      <c r="O27" s="38"/>
+      <c r="P27" s="8"/>
+    </row>
+    <row r="28" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D28" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H28" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M28" s="38"/>
+      <c r="N28" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="O28" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="P28" s="43" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="4:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="D29" s="7">
+        <v>0</v>
+      </c>
+      <c r="E29" s="38">
+        <f>$K$7</f>
+        <v>10</v>
+      </c>
+      <c r="F29" s="38">
+        <f>E29+G29-D29</f>
+        <v>10</v>
+      </c>
+      <c r="G29" s="38">
+        <v>0</v>
+      </c>
+      <c r="H29" s="37">
+        <f>$E$7*F29</f>
+        <v>700</v>
+      </c>
+      <c r="I29" s="38">
+        <f>$E$6*IF(F29&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J29" s="38">
+        <f>D29*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="38">
+        <v>0</v>
+      </c>
+      <c r="L29" s="8">
+        <f>SUM(H29:K29)+$L$18</f>
+        <v>2900</v>
+      </c>
+      <c r="M29" s="38"/>
+      <c r="N29" s="7">
+        <f>IF(F29&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O29" s="38">
+        <f>IF(G29&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P29" s="8">
+        <f>IF(D29&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D30" s="7">
+        <v>5</v>
+      </c>
+      <c r="E30" s="38">
+        <f t="shared" ref="E30:E33" si="8">$K$7</f>
+        <v>10</v>
+      </c>
+      <c r="F30" s="38">
+        <f t="shared" ref="F30:F33" si="9">E30+G30-D30</f>
+        <v>5</v>
+      </c>
+      <c r="G30" s="38">
+        <v>0</v>
+      </c>
+      <c r="H30" s="37">
+        <f t="shared" ref="H30:H33" si="10">$E$7*F30</f>
+        <v>350</v>
+      </c>
+      <c r="I30" s="38">
+        <f t="shared" ref="I30:I33" si="11">$E$6*IF(F30&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J30" s="38">
+        <f t="shared" ref="J30:J33" si="12">D30*$E$9</f>
+        <v>50</v>
+      </c>
+      <c r="K30" s="38">
+        <v>0</v>
+      </c>
+      <c r="L30" s="8">
+        <f>SUM(H30:K30)+$L$18</f>
+        <v>2600</v>
+      </c>
+      <c r="M30" s="38"/>
+      <c r="N30" s="7">
+        <f t="shared" ref="N30:N33" si="13">IF(F30&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O30" s="38">
+        <f t="shared" ref="O30:O33" si="14">IF(G30&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P30" s="8">
+        <f>IF(D30&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D31" s="7">
+        <v>10</v>
+      </c>
+      <c r="E31" s="38">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="F31" s="60">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G31" s="60">
+        <v>0</v>
+      </c>
+      <c r="H31" s="86">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="60">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J31" s="60">
+        <f t="shared" si="12"/>
+        <v>100</v>
+      </c>
+      <c r="K31" s="60">
+        <v>0</v>
+      </c>
+      <c r="L31" s="85">
+        <f>SUM(H31:K31)+$L$18</f>
+        <v>1900</v>
+      </c>
+      <c r="M31" s="38"/>
+      <c r="N31" s="7">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="O31" s="38">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="P31" s="8">
+        <f>IF(D31&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D32" s="44">
+        <v>15</v>
+      </c>
+      <c r="E32" s="45">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="F32" s="45">
+        <f t="shared" si="9"/>
+        <v>-5</v>
+      </c>
+      <c r="G32" s="45">
+        <v>0</v>
+      </c>
+      <c r="H32" s="46">
+        <f t="shared" si="10"/>
+        <v>-350</v>
+      </c>
+      <c r="I32" s="45">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="45">
+        <f t="shared" si="12"/>
+        <v>150</v>
+      </c>
+      <c r="K32" s="45">
+        <v>0</v>
+      </c>
+      <c r="L32" s="47"/>
+      <c r="M32" s="38"/>
+      <c r="N32" s="44">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="O32" s="45">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="P32" s="47">
+        <f>IF(D32&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D33" s="48">
+        <v>20</v>
+      </c>
+      <c r="E33" s="49">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="F33" s="49">
+        <f t="shared" si="9"/>
+        <v>-10</v>
+      </c>
+      <c r="G33" s="49">
+        <v>0</v>
+      </c>
+      <c r="H33" s="50">
+        <f t="shared" si="10"/>
+        <v>-700</v>
+      </c>
+      <c r="I33" s="49">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="49">
+        <f t="shared" si="12"/>
+        <v>200</v>
+      </c>
+      <c r="K33" s="49">
+        <v>0</v>
+      </c>
+      <c r="L33" s="51"/>
+      <c r="M33" s="38"/>
+      <c r="N33" s="48">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="O33" s="49">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="P33" s="51">
+        <f>IF(D33&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D34" s="7"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="38"/>
+      <c r="J34" s="38"/>
+      <c r="K34" s="38"/>
+      <c r="L34" s="38"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="38"/>
+      <c r="O34" s="38"/>
+      <c r="P34" s="8"/>
+    </row>
+    <row r="35" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D35" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="60"/>
+      <c r="J35" s="38"/>
+      <c r="K35" s="38"/>
+      <c r="L35" s="38"/>
+      <c r="M35" s="38"/>
+      <c r="N35" s="38"/>
+      <c r="O35" s="38"/>
+      <c r="P35" s="8"/>
+    </row>
+    <row r="36" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D36" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" s="38">
+        <v>5</v>
+      </c>
+      <c r="F36" s="38"/>
+      <c r="G36" s="38"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="38"/>
+      <c r="J36" s="38"/>
+      <c r="K36" s="38"/>
+      <c r="L36" s="38"/>
+      <c r="M36" s="38"/>
+      <c r="N36" s="38"/>
+      <c r="O36" s="38"/>
+      <c r="P36" s="8"/>
+    </row>
+    <row r="37" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D37" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H37" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M37" s="38"/>
+      <c r="N37" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="O37" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="P37" s="43" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="4:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="D38" s="7">
+        <v>0</v>
+      </c>
+      <c r="E38" s="38">
+        <f>$K$7</f>
+        <v>10</v>
+      </c>
+      <c r="F38" s="38">
+        <f>E38+G38-D38</f>
+        <v>15</v>
+      </c>
+      <c r="G38" s="38">
+        <v>5</v>
+      </c>
+      <c r="H38" s="37">
+        <f>$E$7*F38</f>
+        <v>1050</v>
+      </c>
+      <c r="I38" s="38">
+        <f>$E$6*IF(F38&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J38" s="38">
+        <f>D38*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K38" s="38">
+        <v>0</v>
+      </c>
+      <c r="L38" s="8">
+        <f>SUM(H38:K38)+$L$19</f>
+        <v>2950</v>
+      </c>
+      <c r="M38" s="38"/>
+      <c r="N38" s="7">
+        <f>IF(F38&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O38" s="38">
+        <f>IF(G38&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P38" s="8">
+        <f>IF(D38&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D39" s="7">
+        <v>5</v>
+      </c>
+      <c r="E39" s="38">
+        <f t="shared" ref="E39:E42" si="15">$K$7</f>
+        <v>10</v>
+      </c>
+      <c r="F39" s="38">
+        <f t="shared" ref="F39:F42" si="16">E39+G39-D39</f>
+        <v>10</v>
+      </c>
+      <c r="G39" s="38">
+        <v>5</v>
+      </c>
+      <c r="H39" s="37">
+        <f>$E$7*F39</f>
+        <v>700</v>
+      </c>
+      <c r="I39" s="38">
+        <f>$E$6*IF(F39&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J39" s="38">
+        <f>D39*$E$9</f>
+        <v>50</v>
+      </c>
+      <c r="K39" s="38">
+        <v>0</v>
+      </c>
+      <c r="L39" s="8">
+        <f>SUM(H39:K39)+$L$19</f>
+        <v>2650</v>
+      </c>
+      <c r="M39" s="38"/>
+      <c r="N39" s="7">
+        <f t="shared" ref="N39:N42" si="17">IF(F39&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O39" s="38">
+        <f t="shared" ref="O39:O42" si="18">IF(G39&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P39" s="8">
+        <f>IF(D39&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D40" s="7">
+        <v>10</v>
+      </c>
+      <c r="E40" s="38">
+        <f t="shared" si="15"/>
+        <v>10</v>
+      </c>
+      <c r="F40" s="38">
+        <f t="shared" si="16"/>
+        <v>5</v>
+      </c>
+      <c r="G40" s="38">
+        <v>5</v>
+      </c>
+      <c r="H40" s="37">
+        <f t="shared" ref="H40:H42" si="19">$E$7*F40</f>
+        <v>350</v>
+      </c>
+      <c r="I40" s="38">
+        <f t="shared" ref="I40:I42" si="20">$E$6*IF(F40&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J40" s="38">
+        <f t="shared" ref="J40:J42" si="21">D40*$E$9</f>
+        <v>100</v>
+      </c>
+      <c r="K40" s="38">
+        <v>0</v>
+      </c>
+      <c r="L40" s="8">
+        <f t="shared" ref="L40:L41" si="22">SUM(H40:K40)+$L$19</f>
+        <v>2350</v>
+      </c>
+      <c r="M40" s="38"/>
+      <c r="N40" s="7">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="O40" s="38">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="P40" s="8">
+        <f>IF(D40&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D41" s="7">
+        <v>15</v>
+      </c>
+      <c r="E41" s="38">
+        <f t="shared" si="15"/>
+        <v>10</v>
+      </c>
+      <c r="F41" s="38">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="G41" s="38">
+        <v>5</v>
+      </c>
+      <c r="H41" s="37">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="I41" s="38">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="38">
+        <f t="shared" si="21"/>
+        <v>150</v>
+      </c>
+      <c r="K41" s="38">
+        <v>0</v>
+      </c>
+      <c r="L41" s="8">
+        <f t="shared" si="22"/>
+        <v>1650</v>
+      </c>
+      <c r="M41" s="38"/>
+      <c r="N41" s="7">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="O41" s="38">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="P41" s="8">
+        <f>IF(D41&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D42" s="48">
+        <v>20</v>
+      </c>
+      <c r="E42" s="49">
+        <f t="shared" si="15"/>
+        <v>10</v>
+      </c>
+      <c r="F42" s="49">
+        <f t="shared" si="16"/>
+        <v>-5</v>
+      </c>
+      <c r="G42" s="49">
+        <v>5</v>
+      </c>
+      <c r="H42" s="50">
+        <f t="shared" si="19"/>
+        <v>-350</v>
+      </c>
+      <c r="I42" s="49">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="49">
+        <f t="shared" si="21"/>
+        <v>200</v>
+      </c>
+      <c r="K42" s="49">
+        <v>0</v>
+      </c>
+      <c r="L42" s="51"/>
+      <c r="M42" s="38"/>
+      <c r="N42" s="9">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="O42" s="21">
+        <f t="shared" si="18"/>
+        <v>1</v>
+      </c>
+      <c r="P42" s="10">
+        <f>IF(D42&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D43" s="7"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="38"/>
+      <c r="K43" s="38"/>
+      <c r="L43" s="38"/>
+      <c r="M43" s="38"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="38"/>
+      <c r="P43" s="8"/>
+    </row>
+    <row r="44" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D44" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44" s="38"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="38"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="38"/>
+      <c r="J44" s="38"/>
+      <c r="K44" s="38"/>
+      <c r="L44" s="38"/>
+      <c r="M44" s="38"/>
+      <c r="N44" s="38"/>
+      <c r="O44" s="38"/>
+      <c r="P44" s="8"/>
+    </row>
+    <row r="45" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D45" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E45" s="38">
+        <v>10</v>
+      </c>
+      <c r="F45" s="38"/>
+      <c r="G45" s="38"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="38"/>
+      <c r="J45" s="38"/>
+      <c r="K45" s="38"/>
+      <c r="L45" s="38"/>
+      <c r="M45" s="38"/>
+      <c r="N45" s="38"/>
+      <c r="O45" s="38"/>
+      <c r="P45" s="8"/>
+    </row>
+    <row r="46" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D46" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H46" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J46" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M46" s="38"/>
+      <c r="N46" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="O46" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="P46" s="43" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="4:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="D47" s="7">
+        <v>0</v>
+      </c>
+      <c r="E47" s="38">
+        <f>$K$7</f>
+        <v>10</v>
+      </c>
+      <c r="F47" s="38">
+        <f>E47+G47-D47</f>
+        <v>20</v>
+      </c>
+      <c r="G47" s="38">
+        <v>10</v>
+      </c>
+      <c r="H47" s="37">
+        <f>$E$7*F47</f>
+        <v>1400</v>
+      </c>
+      <c r="I47" s="38">
+        <f>$E$6*IF(F47&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J47" s="38">
+        <f>D47*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K47" s="38">
+        <v>0</v>
+      </c>
+      <c r="L47" s="8">
+        <f>SUM(H47:K47)+$L$20</f>
+        <v>3000</v>
+      </c>
+      <c r="M47" s="38"/>
+      <c r="N47" s="7">
+        <f>IF(F47&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O47" s="38">
+        <f>IF(G47&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P47" s="8">
+        <f>IF(D47&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D48" s="7">
+        <v>5</v>
+      </c>
+      <c r="E48" s="38">
+        <f t="shared" ref="E48:E51" si="23">$K$7</f>
+        <v>10</v>
+      </c>
+      <c r="F48" s="38">
+        <f t="shared" ref="F48:F51" si="24">E48+G48-D48</f>
+        <v>15</v>
+      </c>
+      <c r="G48" s="38">
+        <v>10</v>
+      </c>
+      <c r="H48" s="37">
+        <f t="shared" ref="H48:H51" si="25">$E$7*F48</f>
+        <v>1050</v>
+      </c>
+      <c r="I48" s="38">
+        <f t="shared" ref="I48:I51" si="26">$E$6*IF(F48&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J48" s="38">
+        <f t="shared" ref="J48:J51" si="27">D48*$E$9</f>
+        <v>50</v>
+      </c>
+      <c r="K48" s="38">
+        <v>0</v>
+      </c>
+      <c r="L48" s="8">
+        <f t="shared" ref="L48:L51" si="28">SUM(H48:K48)+$L$20</f>
+        <v>2700</v>
+      </c>
+      <c r="M48" s="38"/>
+      <c r="N48" s="7">
+        <f t="shared" ref="N48:N51" si="29">IF(F48&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O48" s="38">
+        <f t="shared" ref="O48:O51" si="30">IF(G48&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P48" s="8">
+        <f>IF(D48&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D49" s="7">
+        <v>10</v>
+      </c>
+      <c r="E49" s="38">
+        <f t="shared" si="23"/>
+        <v>10</v>
+      </c>
+      <c r="F49" s="38">
+        <f t="shared" si="24"/>
+        <v>10</v>
+      </c>
+      <c r="G49" s="38">
+        <v>10</v>
+      </c>
+      <c r="H49" s="37">
+        <f t="shared" si="25"/>
+        <v>700</v>
+      </c>
+      <c r="I49" s="38">
+        <f t="shared" si="26"/>
+        <v>400</v>
+      </c>
+      <c r="J49" s="38">
+        <f t="shared" si="27"/>
+        <v>100</v>
+      </c>
+      <c r="K49" s="38">
+        <v>0</v>
+      </c>
+      <c r="L49" s="8">
+        <f t="shared" si="28"/>
+        <v>2400</v>
+      </c>
+      <c r="M49" s="38"/>
+      <c r="N49" s="7">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="O49" s="38">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="P49" s="8">
+        <f>IF(D49&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D50" s="7">
+        <v>15</v>
+      </c>
+      <c r="E50" s="38">
+        <f t="shared" si="23"/>
+        <v>10</v>
+      </c>
+      <c r="F50" s="38">
+        <f t="shared" si="24"/>
+        <v>5</v>
+      </c>
+      <c r="G50" s="38">
+        <v>10</v>
+      </c>
+      <c r="H50" s="37">
+        <f t="shared" si="25"/>
+        <v>350</v>
+      </c>
+      <c r="I50" s="38">
+        <f t="shared" si="26"/>
+        <v>400</v>
+      </c>
+      <c r="J50" s="38">
+        <f t="shared" si="27"/>
+        <v>150</v>
+      </c>
+      <c r="K50" s="38">
+        <v>0</v>
+      </c>
+      <c r="L50" s="8">
+        <f t="shared" si="28"/>
+        <v>2100</v>
+      </c>
+      <c r="M50" s="38"/>
+      <c r="N50" s="7">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="O50" s="38">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="P50" s="8">
+        <f>IF(D50&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D51" s="9">
+        <v>20</v>
+      </c>
+      <c r="E51" s="21">
+        <f t="shared" si="23"/>
+        <v>10</v>
+      </c>
+      <c r="F51" s="21">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="G51" s="21">
+        <v>10</v>
+      </c>
+      <c r="H51" s="39">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="21">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="J51" s="21">
+        <f t="shared" si="27"/>
+        <v>200</v>
+      </c>
+      <c r="K51" s="21">
+        <v>0</v>
+      </c>
+      <c r="L51" s="10">
+        <f t="shared" si="28"/>
+        <v>1400</v>
+      </c>
+      <c r="M51" s="38"/>
+      <c r="N51" s="9">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="O51" s="21">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="P51" s="10">
+        <f>IF(D51&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D52" s="7"/>
+      <c r="E52" s="38"/>
+      <c r="F52" s="38"/>
+      <c r="G52" s="38"/>
+      <c r="H52" s="38"/>
+      <c r="I52" s="38"/>
+      <c r="J52" s="38"/>
+      <c r="K52" s="38"/>
+      <c r="L52" s="38"/>
+      <c r="M52" s="38"/>
+      <c r="N52" s="38"/>
+      <c r="O52" s="38"/>
+      <c r="P52" s="8"/>
+    </row>
+    <row r="53" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D53" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E53" s="38"/>
+      <c r="F53" s="38"/>
+      <c r="G53" s="38"/>
+      <c r="H53" s="38"/>
+      <c r="I53" s="38"/>
+      <c r="J53" s="38"/>
+      <c r="K53" s="38"/>
+      <c r="L53" s="38"/>
+      <c r="M53" s="38"/>
+      <c r="N53" s="38"/>
+      <c r="O53" s="38"/>
+      <c r="P53" s="8"/>
+    </row>
+    <row r="54" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D54" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E54" s="38">
+        <v>15</v>
+      </c>
+      <c r="F54" s="38"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="38"/>
+      <c r="I54" s="38"/>
+      <c r="J54" s="38"/>
+      <c r="K54" s="38"/>
+      <c r="L54" s="38"/>
+      <c r="M54" s="38"/>
+      <c r="N54" s="38"/>
+      <c r="O54" s="38"/>
+      <c r="P54" s="8"/>
+    </row>
+    <row r="55" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D55" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G55" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H55" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M55" s="38"/>
+      <c r="N55" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="O55" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="P55" s="43" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="56" spans="4:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="D56" s="7">
+        <v>0</v>
+      </c>
+      <c r="E56" s="38">
+        <f>$K$7</f>
+        <v>10</v>
+      </c>
+      <c r="F56" s="38">
+        <f>E56+G56-D56</f>
+        <v>25</v>
+      </c>
+      <c r="G56" s="38">
+        <v>15</v>
+      </c>
+      <c r="H56" s="37">
+        <f>$E$7*F56</f>
+        <v>1750</v>
+      </c>
+      <c r="I56" s="38">
+        <f>$E$6*IF(F56&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J56" s="38">
+        <f>D56*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K56" s="38">
+        <v>0</v>
+      </c>
+      <c r="L56" s="8">
+        <f>SUM(H56:K56)+$L$21</f>
+        <v>3050</v>
+      </c>
+      <c r="M56" s="38"/>
+      <c r="N56" s="7">
+        <f>IF(F56&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O56" s="38">
+        <f>IF(G56&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P56" s="8">
+        <f>IF(D56&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D57" s="7">
+        <v>5</v>
+      </c>
+      <c r="E57" s="38">
+        <f t="shared" ref="E57:E60" si="31">$K$7</f>
+        <v>10</v>
+      </c>
+      <c r="F57" s="38">
+        <f t="shared" ref="F57:F60" si="32">E57+G57-D57</f>
+        <v>20</v>
+      </c>
+      <c r="G57" s="38">
+        <v>15</v>
+      </c>
+      <c r="H57" s="37">
+        <f t="shared" ref="H57:H60" si="33">$E$7*F57</f>
+        <v>1400</v>
+      </c>
+      <c r="I57" s="38">
+        <f t="shared" ref="I57:I60" si="34">$E$6*IF(F57&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J57" s="38">
+        <f t="shared" ref="J57:J60" si="35">D57*$E$9</f>
+        <v>50</v>
+      </c>
+      <c r="K57" s="38">
+        <v>0</v>
+      </c>
+      <c r="L57" s="8">
+        <f t="shared" ref="L57:L60" si="36">SUM(H57:K57)+$L$21</f>
+        <v>2750</v>
+      </c>
+      <c r="M57" s="38"/>
+      <c r="N57" s="7">
+        <f t="shared" ref="N57:N60" si="37">IF(F57&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O57" s="38">
+        <f t="shared" ref="O57:O60" si="38">IF(G57&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P57" s="8">
+        <f>IF(D57&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D58" s="7">
+        <v>10</v>
+      </c>
+      <c r="E58" s="38">
+        <f t="shared" si="31"/>
+        <v>10</v>
+      </c>
+      <c r="F58" s="38">
+        <f t="shared" si="32"/>
+        <v>15</v>
+      </c>
+      <c r="G58" s="38">
+        <v>15</v>
+      </c>
+      <c r="H58" s="37">
+        <f t="shared" si="33"/>
+        <v>1050</v>
+      </c>
+      <c r="I58" s="38">
+        <f t="shared" si="34"/>
+        <v>400</v>
+      </c>
+      <c r="J58" s="38">
+        <f t="shared" si="35"/>
+        <v>100</v>
+      </c>
+      <c r="K58" s="38">
+        <v>0</v>
+      </c>
+      <c r="L58" s="8">
+        <f t="shared" si="36"/>
+        <v>2450</v>
+      </c>
+      <c r="M58" s="38"/>
+      <c r="N58" s="7">
+        <f t="shared" si="37"/>
+        <v>1</v>
+      </c>
+      <c r="O58" s="38">
+        <f>IF(G58&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P58" s="8">
+        <f>IF(D58&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D59" s="7">
+        <v>15</v>
+      </c>
+      <c r="E59" s="38">
+        <f t="shared" si="31"/>
+        <v>10</v>
+      </c>
+      <c r="F59" s="38">
+        <f t="shared" si="32"/>
+        <v>10</v>
+      </c>
+      <c r="G59" s="38">
+        <v>15</v>
+      </c>
+      <c r="H59" s="37">
+        <f t="shared" si="33"/>
+        <v>700</v>
+      </c>
+      <c r="I59" s="38">
+        <f t="shared" si="34"/>
+        <v>400</v>
+      </c>
+      <c r="J59" s="38">
+        <f t="shared" si="35"/>
+        <v>150</v>
+      </c>
+      <c r="K59" s="38">
+        <v>0</v>
+      </c>
+      <c r="L59" s="8">
+        <f t="shared" si="36"/>
+        <v>2150</v>
+      </c>
+      <c r="M59" s="38"/>
+      <c r="N59" s="7">
+        <f t="shared" si="37"/>
+        <v>1</v>
+      </c>
+      <c r="O59" s="38">
+        <f t="shared" si="38"/>
+        <v>1</v>
+      </c>
+      <c r="P59" s="8">
+        <f>IF(D59&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D60" s="9">
+        <v>20</v>
+      </c>
+      <c r="E60" s="21">
+        <f t="shared" si="31"/>
+        <v>10</v>
+      </c>
+      <c r="F60" s="21">
+        <f t="shared" si="32"/>
+        <v>5</v>
+      </c>
+      <c r="G60" s="21">
+        <v>15</v>
+      </c>
+      <c r="H60" s="39">
+        <f t="shared" si="33"/>
+        <v>350</v>
+      </c>
+      <c r="I60" s="21">
+        <f t="shared" si="34"/>
+        <v>400</v>
+      </c>
+      <c r="J60" s="21">
+        <f t="shared" si="35"/>
+        <v>200</v>
+      </c>
+      <c r="K60" s="21">
+        <v>0</v>
+      </c>
+      <c r="L60" s="10">
+        <f t="shared" si="36"/>
+        <v>1850</v>
+      </c>
+      <c r="M60" s="38"/>
+      <c r="N60" s="9">
+        <f t="shared" si="37"/>
+        <v>1</v>
+      </c>
+      <c r="O60" s="21">
+        <f t="shared" si="38"/>
+        <v>1</v>
+      </c>
+      <c r="P60" s="10">
+        <f>IF(D60&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D61" s="7"/>
+      <c r="E61" s="38"/>
+      <c r="F61" s="38"/>
+      <c r="G61" s="38"/>
+      <c r="H61" s="38"/>
+      <c r="I61" s="38"/>
+      <c r="J61" s="38"/>
+      <c r="K61" s="38"/>
+      <c r="L61" s="38"/>
+      <c r="M61" s="38"/>
+      <c r="N61" s="38"/>
+      <c r="O61" s="38"/>
+      <c r="P61" s="8"/>
+    </row>
+    <row r="62" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D62" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E62" s="38"/>
+      <c r="F62" s="38"/>
+      <c r="G62" s="38"/>
+      <c r="H62" s="38"/>
+      <c r="I62" s="38"/>
+      <c r="J62" s="38"/>
+      <c r="K62" s="38"/>
+      <c r="L62" s="38"/>
+      <c r="M62" s="38"/>
+      <c r="N62" s="38"/>
+      <c r="O62" s="38"/>
+      <c r="P62" s="8"/>
+    </row>
+    <row r="63" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D63" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E63" s="38">
+        <v>20</v>
+      </c>
+      <c r="F63" s="38"/>
+      <c r="G63" s="38"/>
+      <c r="H63" s="38"/>
+      <c r="I63" s="38"/>
+      <c r="J63" s="38"/>
+      <c r="K63" s="38"/>
+      <c r="L63" s="38"/>
+      <c r="M63" s="38"/>
+      <c r="N63" s="38"/>
+      <c r="O63" s="38"/>
+      <c r="P63" s="8"/>
+    </row>
+    <row r="64" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D64" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G64" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H64" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="I64" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J64" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K64" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M64" s="38"/>
+      <c r="N64" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="O64" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="P64" s="43" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="65" spans="4:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="D65" s="7">
+        <v>0</v>
+      </c>
+      <c r="E65" s="38">
+        <f>$K$7</f>
+        <v>10</v>
+      </c>
+      <c r="F65" s="74">
+        <f>E65+G65-D65</f>
+        <v>30</v>
+      </c>
+      <c r="G65" s="38">
+        <v>20</v>
+      </c>
+      <c r="H65" s="37">
+        <f>$E$7*F65</f>
+        <v>2100</v>
+      </c>
+      <c r="I65" s="38">
+        <f>$E$6*IF(F65&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J65" s="38">
+        <f>D65*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K65" s="38">
+        <v>0</v>
+      </c>
+      <c r="L65" s="36">
+        <f>SUM(H65:K65)+$L$22</f>
+        <v>2700</v>
+      </c>
+      <c r="M65" s="38"/>
+      <c r="N65" s="7">
+        <f>IF(F65&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O65" s="38">
+        <f>IF(G65&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P65" s="8">
+        <f>IF(D65&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D66" s="7">
+        <v>5</v>
+      </c>
+      <c r="E66" s="38">
+        <f t="shared" ref="E66:E69" si="39">$K$7</f>
+        <v>10</v>
+      </c>
+      <c r="F66" s="38">
+        <f t="shared" ref="F66:F69" si="40">E66+G66-D66</f>
+        <v>25</v>
+      </c>
+      <c r="G66" s="38">
+        <v>20</v>
+      </c>
+      <c r="H66" s="37">
+        <f t="shared" ref="H66:H69" si="41">$E$7*F66</f>
+        <v>1750</v>
+      </c>
+      <c r="I66" s="38">
+        <f t="shared" ref="I66:I69" si="42">$E$6*IF(F66&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J66" s="38">
+        <f t="shared" ref="J66:J69" si="43">D66*$E$9</f>
+        <v>50</v>
+      </c>
+      <c r="K66" s="38">
+        <v>0</v>
+      </c>
+      <c r="L66" s="8">
+        <f t="shared" ref="L66:L69" si="44">SUM(H66:K66)+$L$22</f>
+        <v>2400</v>
+      </c>
+      <c r="M66" s="38"/>
+      <c r="N66" s="7">
+        <f t="shared" ref="N66:N69" si="45">IF(F66&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O66" s="38">
+        <f t="shared" ref="O66" si="46">IF(G66&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P66" s="8">
+        <f>IF(D66&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D67" s="7">
+        <v>10</v>
+      </c>
+      <c r="E67" s="38">
+        <f t="shared" si="39"/>
+        <v>10</v>
+      </c>
+      <c r="F67" s="38">
+        <f t="shared" si="40"/>
+        <v>20</v>
+      </c>
+      <c r="G67" s="38">
+        <v>20</v>
+      </c>
+      <c r="H67" s="37">
+        <f t="shared" si="41"/>
+        <v>1400</v>
+      </c>
+      <c r="I67" s="38">
+        <f t="shared" si="42"/>
+        <v>400</v>
+      </c>
+      <c r="J67" s="38">
+        <f t="shared" si="43"/>
+        <v>100</v>
+      </c>
+      <c r="K67" s="38">
+        <v>0</v>
+      </c>
+      <c r="L67" s="8">
+        <f t="shared" si="44"/>
+        <v>2100</v>
+      </c>
+      <c r="M67" s="38"/>
+      <c r="N67" s="7">
+        <f t="shared" si="45"/>
+        <v>1</v>
+      </c>
+      <c r="O67" s="38">
+        <f>IF(G67&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P67" s="8">
+        <f>IF(D67&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D68" s="7">
+        <v>15</v>
+      </c>
+      <c r="E68" s="38">
+        <f t="shared" si="39"/>
+        <v>10</v>
+      </c>
+      <c r="F68" s="38">
+        <f t="shared" si="40"/>
+        <v>15</v>
+      </c>
+      <c r="G68" s="38">
+        <v>20</v>
+      </c>
+      <c r="H68" s="37">
+        <f t="shared" si="41"/>
+        <v>1050</v>
+      </c>
+      <c r="I68" s="38">
+        <f t="shared" si="42"/>
+        <v>400</v>
+      </c>
+      <c r="J68" s="38">
+        <f t="shared" si="43"/>
+        <v>150</v>
+      </c>
+      <c r="K68" s="38">
+        <v>0</v>
+      </c>
+      <c r="L68" s="8">
+        <f t="shared" si="44"/>
+        <v>1800</v>
+      </c>
+      <c r="M68" s="38"/>
+      <c r="N68" s="7">
+        <f t="shared" si="45"/>
+        <v>1</v>
+      </c>
+      <c r="O68" s="38">
+        <f t="shared" ref="O68:O69" si="47">IF(G68&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P68" s="8">
+        <f>IF(D68&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D69" s="9">
+        <v>20</v>
+      </c>
+      <c r="E69" s="21">
+        <f t="shared" si="39"/>
+        <v>10</v>
+      </c>
+      <c r="F69" s="21">
+        <f t="shared" si="40"/>
+        <v>10</v>
+      </c>
+      <c r="G69" s="21">
+        <v>20</v>
+      </c>
+      <c r="H69" s="39">
+        <f t="shared" si="41"/>
+        <v>700</v>
+      </c>
+      <c r="I69" s="21">
+        <f t="shared" si="42"/>
+        <v>400</v>
+      </c>
+      <c r="J69" s="21">
+        <f t="shared" si="43"/>
+        <v>200</v>
+      </c>
+      <c r="K69" s="21">
+        <v>0</v>
+      </c>
+      <c r="L69" s="10">
+        <f t="shared" si="44"/>
+        <v>1500</v>
+      </c>
+      <c r="M69" s="38"/>
+      <c r="N69" s="9">
+        <f t="shared" si="45"/>
+        <v>1</v>
+      </c>
+      <c r="O69" s="21">
+        <f t="shared" si="47"/>
+        <v>1</v>
+      </c>
+      <c r="P69" s="10">
+        <f>IF(D69&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D70" s="7"/>
+      <c r="E70" s="38"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="38"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="38"/>
+      <c r="J70" s="38"/>
+      <c r="K70" s="38"/>
+      <c r="L70" s="38"/>
+      <c r="M70" s="38"/>
+      <c r="N70" s="38"/>
+      <c r="O70" s="38"/>
+      <c r="P70" s="8"/>
+    </row>
+    <row r="71" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D71" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E71" s="24"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="38"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="38"/>
+      <c r="J71" s="38"/>
+      <c r="K71" s="38"/>
+      <c r="L71" s="38"/>
+      <c r="M71" s="38"/>
+      <c r="N71" s="38"/>
+      <c r="O71" s="38"/>
+      <c r="P71" s="8"/>
+    </row>
+    <row r="72" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D72" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F72" s="38"/>
+      <c r="G72" s="38"/>
+      <c r="H72" s="38"/>
+      <c r="I72" s="38"/>
+      <c r="J72" s="38"/>
+      <c r="K72" s="38"/>
+      <c r="L72" s="38"/>
+      <c r="M72" s="38"/>
+      <c r="N72" s="38"/>
+      <c r="O72" s="38"/>
+      <c r="P72" s="8"/>
+    </row>
+    <row r="73" spans="4:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="D73" s="77">
+        <v>0</v>
+      </c>
+      <c r="E73" s="36">
+        <f>MIN(L29,L38,L47,L56,L65)</f>
+        <v>2700</v>
+      </c>
+      <c r="F73" s="38"/>
+      <c r="G73" s="38"/>
+      <c r="H73" s="38"/>
+      <c r="I73" s="38"/>
+      <c r="J73" s="38"/>
+      <c r="K73" s="38"/>
+      <c r="L73" s="38"/>
+      <c r="M73" s="38"/>
+      <c r="N73" s="38"/>
+      <c r="O73" s="38"/>
+      <c r="P73" s="8"/>
+    </row>
+    <row r="74" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D74" s="7">
+        <v>5</v>
+      </c>
+      <c r="E74" s="8">
+        <f t="shared" ref="E74:E77" si="48">MIN(L30,L39,L48,L57,L66)</f>
+        <v>2400</v>
+      </c>
+      <c r="F74" s="38"/>
+      <c r="G74" s="38"/>
+      <c r="H74" s="38"/>
+      <c r="I74" s="38"/>
+      <c r="J74" s="38"/>
+      <c r="K74" s="38"/>
+      <c r="L74" s="38"/>
+      <c r="M74" s="38"/>
+      <c r="N74" s="38"/>
+      <c r="O74" s="38"/>
+      <c r="P74" s="8"/>
+    </row>
+    <row r="75" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D75" s="84">
+        <v>10</v>
+      </c>
+      <c r="E75" s="85">
+        <f>MIN(L31,L40,L49,L58,L67)</f>
+        <v>1900</v>
+      </c>
+      <c r="F75" s="38"/>
+      <c r="G75" s="38"/>
+      <c r="H75" s="38"/>
+      <c r="I75" s="38"/>
+      <c r="J75" s="38"/>
+      <c r="K75" s="38"/>
+      <c r="L75" s="38"/>
+      <c r="M75" s="38"/>
+      <c r="N75" s="38"/>
+      <c r="O75" s="38"/>
+      <c r="P75" s="8"/>
+    </row>
+    <row r="76" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D76" s="7">
+        <v>15</v>
+      </c>
+      <c r="E76" s="8">
+        <f t="shared" si="48"/>
+        <v>1650</v>
+      </c>
+      <c r="F76" s="38"/>
+      <c r="G76" s="38"/>
+      <c r="H76" s="38"/>
+      <c r="I76" s="38"/>
+      <c r="J76" s="38"/>
+      <c r="K76" s="38"/>
+      <c r="L76" s="38"/>
+      <c r="M76" s="38"/>
+      <c r="N76" s="38"/>
+      <c r="O76" s="38"/>
+      <c r="P76" s="8"/>
+    </row>
+    <row r="77" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D77" s="9">
+        <v>20</v>
+      </c>
+      <c r="E77" s="10">
+        <f t="shared" si="48"/>
+        <v>1400</v>
+      </c>
+      <c r="F77" s="21"/>
+      <c r="G77" s="21"/>
+      <c r="H77" s="21"/>
+      <c r="I77" s="21"/>
+      <c r="J77" s="21"/>
+      <c r="K77" s="21"/>
+      <c r="L77" s="21"/>
+      <c r="M77" s="21"/>
+      <c r="N77" s="21"/>
+      <c r="O77" s="21"/>
+      <c r="P77" s="10"/>
+    </row>
+    <row r="79" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="80" spans="4:16" x14ac:dyDescent="0.35">
+      <c r="D80" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E80" s="32"/>
+      <c r="F80" s="32"/>
+      <c r="G80" s="32"/>
+      <c r="H80" s="32"/>
+      <c r="I80" s="32"/>
+      <c r="J80" s="32"/>
+      <c r="K80" s="32"/>
+      <c r="L80" s="32"/>
+      <c r="M80" s="32"/>
+      <c r="N80" s="32"/>
+      <c r="O80" s="32"/>
+      <c r="P80" s="24"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="D81" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E81" s="38"/>
+      <c r="F81" s="38"/>
+      <c r="G81" s="38"/>
+      <c r="H81" s="38"/>
+      <c r="I81" s="38"/>
+      <c r="J81" s="38"/>
+      <c r="K81" s="38"/>
+      <c r="L81" s="38"/>
+      <c r="M81" s="38"/>
+      <c r="N81" s="38"/>
+      <c r="O81" s="38"/>
+      <c r="P81" s="8"/>
+    </row>
+    <row r="82" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D82" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E82" s="38">
+        <v>0</v>
+      </c>
+      <c r="F82" s="38"/>
+      <c r="G82" s="38"/>
+      <c r="H82" s="38"/>
+      <c r="I82" s="38"/>
+      <c r="J82" s="38"/>
+      <c r="K82" s="38"/>
+      <c r="L82" s="38"/>
+      <c r="M82" s="38"/>
+      <c r="N82" s="38"/>
+      <c r="O82" s="38"/>
+      <c r="P82" s="8"/>
+    </row>
+    <row r="83" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D83" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F83" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H83" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="I83" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K83" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L83" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M83" s="38"/>
+      <c r="N83" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="O83" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="P83" s="43" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="D84" s="44">
+        <v>0</v>
+      </c>
+      <c r="E84" s="45">
+        <f>$K$6</f>
+        <v>50</v>
+      </c>
+      <c r="F84" s="45">
+        <f>E84+G84-D84</f>
+        <v>50</v>
+      </c>
+      <c r="G84" s="45">
+        <v>0</v>
+      </c>
+      <c r="H84" s="46">
+        <f>$E$7*F84</f>
+        <v>3500</v>
+      </c>
+      <c r="I84" s="45">
+        <f>$E$6*IF(F84&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J84" s="45">
+        <f>D84*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K84" s="45">
+        <v>0</v>
+      </c>
+      <c r="L84" s="47"/>
+      <c r="M84" s="45"/>
+      <c r="N84" s="44">
+        <f>IF(F84&lt;=$E$4,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O84" s="45">
+        <f>IF(G84&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P84" s="47">
+        <f>IF(D84&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="D85" s="44">
+        <v>5</v>
+      </c>
+      <c r="E85" s="45">
+        <f t="shared" ref="E85:E88" si="49">$K$6</f>
+        <v>50</v>
+      </c>
+      <c r="F85" s="45">
+        <f t="shared" ref="F85:F86" si="50">E85+G85-D85</f>
+        <v>45</v>
+      </c>
+      <c r="G85" s="45">
+        <v>0</v>
+      </c>
+      <c r="H85" s="46">
+        <f t="shared" ref="H85:H86" si="51">$E$7*F85</f>
+        <v>3150</v>
+      </c>
+      <c r="I85" s="45">
+        <f t="shared" ref="I85:I86" si="52">$E$6*IF(F85&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J85" s="45">
+        <f t="shared" ref="J85:J88" si="53">D85*$E$9</f>
+        <v>50</v>
+      </c>
+      <c r="K85" s="45">
+        <v>0</v>
+      </c>
+      <c r="L85" s="47"/>
+      <c r="M85" s="45"/>
+      <c r="N85" s="44">
+        <f t="shared" ref="N85:N88" si="54">IF(F85&lt;=$E$4,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O85" s="45">
+        <f t="shared" ref="O85:O88" si="55">IF(G85&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P85" s="47">
+        <f>IF(D85&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="D86" s="7">
+        <v>10</v>
+      </c>
+      <c r="E86" s="38">
+        <f t="shared" si="49"/>
+        <v>50</v>
+      </c>
+      <c r="F86" s="74">
+        <f t="shared" si="50"/>
+        <v>40</v>
+      </c>
+      <c r="G86" s="38">
+        <v>0</v>
+      </c>
+      <c r="H86" s="37">
+        <f t="shared" si="51"/>
+        <v>2800</v>
+      </c>
+      <c r="I86" s="38">
+        <f t="shared" si="52"/>
+        <v>400</v>
+      </c>
+      <c r="J86" s="38">
+        <f t="shared" si="53"/>
+        <v>100</v>
+      </c>
+      <c r="K86" s="38">
+        <v>0</v>
+      </c>
+      <c r="L86" s="36">
+        <f>SUM(H86:K86)+$E$73</f>
+        <v>6000</v>
+      </c>
+      <c r="M86" s="38"/>
+      <c r="N86" s="7">
+        <f t="shared" si="54"/>
+        <v>1</v>
+      </c>
+      <c r="O86" s="38">
+        <f t="shared" si="55"/>
+        <v>1</v>
+      </c>
+      <c r="P86" s="8">
+        <f>IF(D86&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C87" s="61"/>
+      <c r="D87" s="53">
+        <v>15</v>
+      </c>
+      <c r="E87" s="54">
+        <f t="shared" si="49"/>
+        <v>50</v>
+      </c>
+      <c r="F87" s="54">
+        <f t="shared" ref="F87:F88" si="56">E87+G87-D87</f>
+        <v>35</v>
+      </c>
+      <c r="G87" s="54">
+        <v>0</v>
+      </c>
+      <c r="H87" s="62">
+        <f t="shared" ref="H87:H88" si="57">$E$7*F87</f>
+        <v>2450</v>
+      </c>
+      <c r="I87" s="54">
+        <f t="shared" ref="I87:I88" si="58">$E$6*IF(F87&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J87" s="54">
+        <f t="shared" ref="J87:J88" si="59">D87*$E$9</f>
+        <v>150</v>
+      </c>
+      <c r="K87" s="54">
+        <v>0</v>
+      </c>
+      <c r="L87" s="55">
+        <f t="shared" ref="L87:L88" si="60">SUM(H87:K87)+$E$73</f>
+        <v>5700</v>
+      </c>
+      <c r="M87" s="54"/>
+      <c r="N87" s="53">
+        <f t="shared" si="54"/>
+        <v>1</v>
+      </c>
+      <c r="O87" s="54">
+        <f t="shared" si="55"/>
+        <v>1</v>
+      </c>
+      <c r="P87" s="55">
+        <f>IF(D87&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C88" s="61"/>
+      <c r="D88" s="56">
+        <v>20</v>
+      </c>
+      <c r="E88" s="57">
+        <f t="shared" si="49"/>
+        <v>50</v>
+      </c>
+      <c r="F88" s="57">
+        <f t="shared" si="56"/>
+        <v>30</v>
+      </c>
+      <c r="G88" s="57">
+        <v>0</v>
+      </c>
+      <c r="H88" s="59">
+        <f t="shared" si="57"/>
+        <v>2100</v>
+      </c>
+      <c r="I88" s="57">
+        <f t="shared" si="58"/>
+        <v>400</v>
+      </c>
+      <c r="J88" s="57">
+        <f t="shared" si="59"/>
+        <v>200</v>
+      </c>
+      <c r="K88" s="57">
+        <v>0</v>
+      </c>
+      <c r="L88" s="58">
+        <f t="shared" si="60"/>
+        <v>5400</v>
+      </c>
+      <c r="M88" s="54"/>
+      <c r="N88" s="56">
+        <f t="shared" si="54"/>
+        <v>1</v>
+      </c>
+      <c r="O88" s="57">
+        <f t="shared" si="55"/>
+        <v>1</v>
+      </c>
+      <c r="P88" s="58">
+        <f>IF(D88&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C89" s="61"/>
+      <c r="D89" s="53"/>
+      <c r="E89" s="54"/>
+      <c r="F89" s="54"/>
+      <c r="G89" s="54"/>
+      <c r="H89" s="54"/>
+      <c r="I89" s="54"/>
+      <c r="J89" s="54"/>
+      <c r="K89" s="54"/>
+      <c r="L89" s="54"/>
+      <c r="M89" s="54"/>
+      <c r="N89" s="54"/>
+      <c r="O89" s="54"/>
+      <c r="P89" s="55"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C90" s="61"/>
+      <c r="D90" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="E90" s="54"/>
+      <c r="F90" s="54"/>
+      <c r="G90" s="54"/>
+      <c r="H90" s="54"/>
+      <c r="I90" s="54"/>
+      <c r="J90" s="54"/>
+      <c r="K90" s="54"/>
+      <c r="L90" s="54"/>
+      <c r="M90" s="54"/>
+      <c r="N90" s="54"/>
+      <c r="O90" s="54"/>
+      <c r="P90" s="55"/>
+    </row>
+    <row r="91" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C91" s="61"/>
+      <c r="D91" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="E91" s="54">
+        <v>5</v>
+      </c>
+      <c r="F91" s="54"/>
+      <c r="G91" s="54"/>
+      <c r="H91" s="54"/>
+      <c r="I91" s="54"/>
+      <c r="J91" s="54"/>
+      <c r="K91" s="54"/>
+      <c r="L91" s="54"/>
+      <c r="M91" s="54"/>
+      <c r="N91" s="54"/>
+      <c r="O91" s="54"/>
+      <c r="P91" s="55"/>
+    </row>
+    <row r="92" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C92" s="61"/>
+      <c r="D92" s="63" t="s">
+        <v>51</v>
+      </c>
+      <c r="E92" s="64" t="s">
+        <v>66</v>
+      </c>
+      <c r="F92" s="64" t="s">
+        <v>69</v>
+      </c>
+      <c r="G92" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="H92" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="I92" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="J92" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="K92" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="L92" s="66" t="s">
+        <v>100</v>
+      </c>
+      <c r="M92" s="54"/>
+      <c r="N92" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="O92" s="68" t="s">
+        <v>102</v>
+      </c>
+      <c r="P92" s="69" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="C93" s="61"/>
+      <c r="D93" s="44">
+        <v>0</v>
+      </c>
+      <c r="E93" s="45">
+        <f>$K$6</f>
+        <v>50</v>
+      </c>
+      <c r="F93" s="45">
+        <f>E93+G93-D93</f>
+        <v>55</v>
+      </c>
+      <c r="G93" s="45">
+        <v>5</v>
+      </c>
+      <c r="H93" s="46">
+        <f>$E$7*F93</f>
+        <v>3850</v>
+      </c>
+      <c r="I93" s="45">
+        <f>$E$6*IF(F93&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J93" s="45">
+        <f>D93*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K93" s="45">
+        <v>0</v>
+      </c>
+      <c r="L93" s="47"/>
+      <c r="M93" s="45"/>
+      <c r="N93" s="44">
+        <f>IF(F93&lt;=$E$4,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O93" s="45">
+        <f>IF(G93&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P93" s="47">
+        <f>IF(D93&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C94" s="61"/>
+      <c r="D94" s="44">
+        <v>5</v>
+      </c>
+      <c r="E94" s="45">
+        <f t="shared" ref="E94:E97" si="61">$K$6</f>
+        <v>50</v>
+      </c>
+      <c r="F94" s="45">
+        <f t="shared" ref="F94:F97" si="62">E94+G94-D94</f>
+        <v>50</v>
+      </c>
+      <c r="G94" s="45">
+        <v>5</v>
+      </c>
+      <c r="H94" s="46">
+        <f t="shared" ref="H94:H97" si="63">$E$7*F94</f>
+        <v>3500</v>
+      </c>
+      <c r="I94" s="45">
+        <f t="shared" ref="I94:I97" si="64">$E$6*IF(F94&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J94" s="45">
+        <f t="shared" ref="J94:J97" si="65">D94*$E$9</f>
+        <v>50</v>
+      </c>
+      <c r="K94" s="45">
+        <v>0</v>
+      </c>
+      <c r="L94" s="47"/>
+      <c r="M94" s="45"/>
+      <c r="N94" s="44">
+        <f t="shared" ref="N94:N97" si="66">IF(F94&lt;=$E$4,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O94" s="45">
+        <f t="shared" ref="O94:O97" si="67">IF(G94&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P94" s="47">
+        <f>IF(D94&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C95" s="61"/>
+      <c r="D95" s="44">
+        <v>10</v>
+      </c>
+      <c r="E95" s="45">
+        <f t="shared" si="61"/>
+        <v>50</v>
+      </c>
+      <c r="F95" s="45">
+        <f t="shared" si="62"/>
+        <v>45</v>
+      </c>
+      <c r="G95" s="45">
+        <v>5</v>
+      </c>
+      <c r="H95" s="46">
+        <f t="shared" si="63"/>
+        <v>3150</v>
+      </c>
+      <c r="I95" s="45">
+        <f t="shared" si="64"/>
+        <v>400</v>
+      </c>
+      <c r="J95" s="45">
+        <f t="shared" si="65"/>
+        <v>100</v>
+      </c>
+      <c r="K95" s="45">
+        <v>0</v>
+      </c>
+      <c r="L95" s="47"/>
+      <c r="M95" s="45"/>
+      <c r="N95" s="44">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
+      <c r="O95" s="45">
+        <f t="shared" si="67"/>
+        <v>1</v>
+      </c>
+      <c r="P95" s="47">
+        <f>IF(D95&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C96" s="61"/>
+      <c r="D96" s="53">
+        <v>15</v>
+      </c>
+      <c r="E96" s="54">
+        <f t="shared" si="61"/>
+        <v>50</v>
+      </c>
+      <c r="F96" s="54">
+        <f t="shared" si="62"/>
+        <v>40</v>
+      </c>
+      <c r="G96" s="54">
+        <v>5</v>
+      </c>
+      <c r="H96" s="62">
+        <f t="shared" si="63"/>
+        <v>2800</v>
+      </c>
+      <c r="I96" s="54">
+        <f t="shared" si="64"/>
+        <v>400</v>
+      </c>
+      <c r="J96" s="54">
+        <f t="shared" si="65"/>
+        <v>150</v>
+      </c>
+      <c r="K96" s="54">
+        <v>0</v>
+      </c>
+      <c r="L96" s="55">
+        <f>SUM(H96:K96)+$E$74</f>
+        <v>5750</v>
+      </c>
+      <c r="M96" s="54"/>
+      <c r="N96" s="53">
+        <f t="shared" si="66"/>
+        <v>1</v>
+      </c>
+      <c r="O96" s="54">
+        <f t="shared" si="67"/>
+        <v>1</v>
+      </c>
+      <c r="P96" s="55">
+        <f>IF(D96&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C97" s="61"/>
+      <c r="D97" s="56">
+        <v>20</v>
+      </c>
+      <c r="E97" s="57">
+        <f t="shared" si="61"/>
+        <v>50</v>
+      </c>
+      <c r="F97" s="57">
+        <f t="shared" si="62"/>
+        <v>35</v>
+      </c>
+      <c r="G97" s="57">
+        <v>5</v>
+      </c>
+      <c r="H97" s="59">
+        <f t="shared" si="63"/>
+        <v>2450</v>
+      </c>
+      <c r="I97" s="57">
+        <f t="shared" si="64"/>
+        <v>400</v>
+      </c>
+      <c r="J97" s="57">
+        <f t="shared" si="65"/>
+        <v>200</v>
+      </c>
+      <c r="K97" s="57">
+        <v>0</v>
+      </c>
+      <c r="L97" s="58">
+        <f>SUM(H97:K97)+$E$74</f>
+        <v>5450</v>
+      </c>
+      <c r="M97" s="54"/>
+      <c r="N97" s="56">
+        <f t="shared" si="66"/>
+        <v>1</v>
+      </c>
+      <c r="O97" s="57">
+        <f t="shared" si="67"/>
+        <v>1</v>
+      </c>
+      <c r="P97" s="58">
+        <f>IF(D97&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C98" s="61"/>
+      <c r="D98" s="53"/>
+      <c r="E98" s="54"/>
+      <c r="F98" s="54"/>
+      <c r="G98" s="54"/>
+      <c r="H98" s="54"/>
+      <c r="I98" s="54"/>
+      <c r="J98" s="54"/>
+      <c r="K98" s="54"/>
+      <c r="L98" s="54"/>
+      <c r="M98" s="54"/>
+      <c r="N98" s="54"/>
+      <c r="O98" s="54"/>
+      <c r="P98" s="55"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C99" s="61"/>
+      <c r="D99" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="E99" s="54"/>
+      <c r="F99" s="54"/>
+      <c r="G99" s="54"/>
+      <c r="H99" s="54"/>
+      <c r="I99" s="54"/>
+      <c r="J99" s="54"/>
+      <c r="K99" s="54"/>
+      <c r="L99" s="54"/>
+      <c r="M99" s="54"/>
+      <c r="N99" s="54"/>
+      <c r="O99" s="54"/>
+      <c r="P99" s="55"/>
+    </row>
+    <row r="100" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C100" s="61"/>
+      <c r="D100" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="E100" s="54">
+        <v>10</v>
+      </c>
+      <c r="F100" s="54"/>
+      <c r="G100" s="54"/>
+      <c r="H100" s="54"/>
+      <c r="I100" s="54"/>
+      <c r="J100" s="54"/>
+      <c r="K100" s="54"/>
+      <c r="L100" s="54"/>
+      <c r="M100" s="54"/>
+      <c r="N100" s="54"/>
+      <c r="O100" s="54"/>
+      <c r="P100" s="55"/>
+    </row>
+    <row r="101" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C101" s="61"/>
+      <c r="D101" s="63" t="s">
+        <v>51</v>
+      </c>
+      <c r="E101" s="64" t="s">
+        <v>66</v>
+      </c>
+      <c r="F101" s="64" t="s">
+        <v>69</v>
+      </c>
+      <c r="G101" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="H101" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="I101" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="J101" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="K101" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="L101" s="66" t="s">
+        <v>100</v>
+      </c>
+      <c r="M101" s="54"/>
+      <c r="N101" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="O101" s="68" t="s">
+        <v>102</v>
+      </c>
+      <c r="P101" s="69" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="C102" s="61"/>
+      <c r="D102" s="44">
+        <v>0</v>
+      </c>
+      <c r="E102" s="45">
+        <f>$K$6</f>
+        <v>50</v>
+      </c>
+      <c r="F102" s="45">
+        <f>E102+G102-D102</f>
+        <v>60</v>
+      </c>
+      <c r="G102" s="45">
+        <v>10</v>
+      </c>
+      <c r="H102" s="46">
+        <f>$E$7*F102</f>
+        <v>4200</v>
+      </c>
+      <c r="I102" s="45">
+        <f>$E$6*IF(F102&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J102" s="45">
+        <f>D102*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K102" s="45">
+        <v>0</v>
+      </c>
+      <c r="L102" s="47"/>
+      <c r="M102" s="45"/>
+      <c r="N102" s="44">
+        <f>IF(F102&lt;=$E$4,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O102" s="45">
+        <f>IF(G102&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P102" s="47">
+        <f>IF(D102&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C103" s="61"/>
+      <c r="D103" s="44">
+        <v>5</v>
+      </c>
+      <c r="E103" s="45">
+        <f t="shared" ref="E103:E106" si="68">$K$6</f>
+        <v>50</v>
+      </c>
+      <c r="F103" s="45">
+        <f t="shared" ref="F103:F106" si="69">E103+G103-D103</f>
+        <v>55</v>
+      </c>
+      <c r="G103" s="45">
+        <v>10</v>
+      </c>
+      <c r="H103" s="46">
+        <f t="shared" ref="H103:H106" si="70">$E$7*F103</f>
+        <v>3850</v>
+      </c>
+      <c r="I103" s="45">
+        <f t="shared" ref="I103:I106" si="71">$E$6*IF(F103&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J103" s="45">
+        <f t="shared" ref="J103:J106" si="72">D103*$E$9</f>
+        <v>50</v>
+      </c>
+      <c r="K103" s="45">
+        <v>0</v>
+      </c>
+      <c r="L103" s="47"/>
+      <c r="M103" s="45"/>
+      <c r="N103" s="44">
+        <f t="shared" ref="N103:N106" si="73">IF(F103&lt;=$E$4,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O103" s="45">
+        <f t="shared" ref="O103:O106" si="74">IF(G103&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P103" s="47">
+        <f>IF(D103&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C104" s="61"/>
+      <c r="D104" s="44">
+        <v>10</v>
+      </c>
+      <c r="E104" s="45">
+        <f t="shared" si="68"/>
+        <v>50</v>
+      </c>
+      <c r="F104" s="45">
+        <f t="shared" si="69"/>
+        <v>50</v>
+      </c>
+      <c r="G104" s="45">
+        <v>10</v>
+      </c>
+      <c r="H104" s="46">
+        <f t="shared" si="70"/>
+        <v>3500</v>
+      </c>
+      <c r="I104" s="45">
+        <f t="shared" si="71"/>
+        <v>400</v>
+      </c>
+      <c r="J104" s="45">
+        <f t="shared" si="72"/>
+        <v>100</v>
+      </c>
+      <c r="K104" s="45">
+        <v>0</v>
+      </c>
+      <c r="L104" s="47"/>
+      <c r="M104" s="45"/>
+      <c r="N104" s="44">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="O104" s="45">
+        <f t="shared" si="74"/>
+        <v>1</v>
+      </c>
+      <c r="P104" s="47">
+        <f>IF(D104&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C105" s="61"/>
+      <c r="D105" s="44">
+        <v>15</v>
+      </c>
+      <c r="E105" s="45">
+        <f t="shared" si="68"/>
+        <v>50</v>
+      </c>
+      <c r="F105" s="45">
+        <f t="shared" si="69"/>
+        <v>45</v>
+      </c>
+      <c r="G105" s="45">
+        <v>10</v>
+      </c>
+      <c r="H105" s="46">
+        <f t="shared" si="70"/>
+        <v>3150</v>
+      </c>
+      <c r="I105" s="45">
+        <f t="shared" si="71"/>
+        <v>400</v>
+      </c>
+      <c r="J105" s="45">
+        <f t="shared" si="72"/>
+        <v>150</v>
+      </c>
+      <c r="K105" s="45">
+        <v>0</v>
+      </c>
+      <c r="L105" s="47"/>
+      <c r="M105" s="45"/>
+      <c r="N105" s="44">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
+      <c r="O105" s="45">
+        <f t="shared" si="74"/>
+        <v>1</v>
+      </c>
+      <c r="P105" s="47">
+        <f>IF(D105&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C106" s="61"/>
+      <c r="D106" s="56">
+        <v>20</v>
+      </c>
+      <c r="E106" s="57">
+        <f t="shared" si="68"/>
+        <v>50</v>
+      </c>
+      <c r="F106" s="82">
+        <f t="shared" si="69"/>
+        <v>40</v>
+      </c>
+      <c r="G106" s="82">
+        <v>10</v>
+      </c>
+      <c r="H106" s="83">
+        <f t="shared" si="70"/>
+        <v>2800</v>
+      </c>
+      <c r="I106" s="82">
+        <f t="shared" si="71"/>
+        <v>400</v>
+      </c>
+      <c r="J106" s="82">
+        <f t="shared" si="72"/>
+        <v>200</v>
+      </c>
+      <c r="K106" s="82">
+        <v>0</v>
+      </c>
+      <c r="L106" s="79">
+        <f>SUM(H106:K106)+$E$75</f>
+        <v>5300</v>
+      </c>
+      <c r="M106" s="54"/>
+      <c r="N106" s="56">
+        <f t="shared" si="73"/>
+        <v>1</v>
+      </c>
+      <c r="O106" s="57">
+        <f t="shared" si="74"/>
+        <v>1</v>
+      </c>
+      <c r="P106" s="58">
+        <f>IF(D106&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C107" s="61"/>
+      <c r="D107" s="53"/>
+      <c r="E107" s="54"/>
+      <c r="F107" s="54"/>
+      <c r="G107" s="54"/>
+      <c r="H107" s="54"/>
+      <c r="I107" s="54"/>
+      <c r="J107" s="54"/>
+      <c r="K107" s="54"/>
+      <c r="L107" s="54"/>
+      <c r="M107" s="54"/>
+      <c r="N107" s="54"/>
+      <c r="O107" s="54"/>
+      <c r="P107" s="55"/>
+    </row>
+    <row r="108" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C108" s="61"/>
+      <c r="D108" s="53" t="s">
+        <v>76</v>
+      </c>
+      <c r="E108" s="54"/>
+      <c r="F108" s="54"/>
+      <c r="G108" s="54"/>
+      <c r="H108" s="54"/>
+      <c r="I108" s="54"/>
+      <c r="J108" s="54"/>
+      <c r="K108" s="54"/>
+      <c r="L108" s="54"/>
+      <c r="M108" s="54"/>
+      <c r="N108" s="54"/>
+      <c r="O108" s="54"/>
+      <c r="P108" s="55"/>
+    </row>
+    <row r="109" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C109" s="61"/>
+      <c r="D109" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="E109" s="54">
+        <v>15</v>
+      </c>
+      <c r="F109" s="54"/>
+      <c r="G109" s="54"/>
+      <c r="H109" s="54"/>
+      <c r="I109" s="54"/>
+      <c r="J109" s="54"/>
+      <c r="K109" s="54"/>
+      <c r="L109" s="54"/>
+      <c r="M109" s="54"/>
+      <c r="N109" s="54"/>
+      <c r="O109" s="54"/>
+      <c r="P109" s="55"/>
+    </row>
+    <row r="110" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C110" s="61"/>
+      <c r="D110" s="63" t="s">
+        <v>51</v>
+      </c>
+      <c r="E110" s="64" t="s">
+        <v>66</v>
+      </c>
+      <c r="F110" s="64" t="s">
+        <v>69</v>
+      </c>
+      <c r="G110" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="H110" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="I110" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="J110" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="K110" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="L110" s="66" t="s">
+        <v>100</v>
+      </c>
+      <c r="M110" s="54"/>
+      <c r="N110" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="O110" s="68" t="s">
+        <v>102</v>
+      </c>
+      <c r="P110" s="69" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="111" spans="3:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="C111" s="61"/>
+      <c r="D111" s="44">
+        <v>0</v>
+      </c>
+      <c r="E111" s="45">
+        <f>$K$6</f>
+        <v>50</v>
+      </c>
+      <c r="F111" s="45">
+        <f>E111+G111-D111</f>
+        <v>65</v>
+      </c>
+      <c r="G111" s="45">
+        <v>15</v>
+      </c>
+      <c r="H111" s="46">
+        <f>$E$7*F111</f>
+        <v>4550</v>
+      </c>
+      <c r="I111" s="45">
+        <f>$E$6*IF(F111&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J111" s="45">
+        <f>D111*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K111" s="45">
+        <v>0</v>
+      </c>
+      <c r="L111" s="47"/>
+      <c r="M111" s="45"/>
+      <c r="N111" s="44">
+        <f>IF(F111&lt;=$E$4,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O111" s="45">
+        <f>IF(G111&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P111" s="47">
+        <f>IF(D111&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C112" s="61"/>
+      <c r="D112" s="44">
+        <v>5</v>
+      </c>
+      <c r="E112" s="45">
+        <f t="shared" ref="E112:E115" si="75">$K$6</f>
+        <v>50</v>
+      </c>
+      <c r="F112" s="45">
+        <f t="shared" ref="F112:F115" si="76">E112+G112-D112</f>
+        <v>60</v>
+      </c>
+      <c r="G112" s="45">
+        <v>15</v>
+      </c>
+      <c r="H112" s="46">
+        <f t="shared" ref="H112:H115" si="77">$E$7*F112</f>
+        <v>4200</v>
+      </c>
+      <c r="I112" s="45">
+        <f t="shared" ref="I112:I115" si="78">$E$6*IF(F112&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J112" s="45">
+        <f t="shared" ref="J112:J115" si="79">D112*$E$9</f>
+        <v>50</v>
+      </c>
+      <c r="K112" s="45">
+        <v>0</v>
+      </c>
+      <c r="L112" s="47"/>
+      <c r="M112" s="45"/>
+      <c r="N112" s="44">
+        <f t="shared" ref="N112:N115" si="80">IF(F112&lt;=$E$4,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O112" s="45">
+        <f t="shared" ref="O112:O115" si="81">IF(G112&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P112" s="47">
+        <f>IF(D112&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C113" s="61"/>
+      <c r="D113" s="44">
+        <v>10</v>
+      </c>
+      <c r="E113" s="45">
+        <f t="shared" si="75"/>
+        <v>50</v>
+      </c>
+      <c r="F113" s="45">
+        <f t="shared" si="76"/>
+        <v>55</v>
+      </c>
+      <c r="G113" s="45">
+        <v>15</v>
+      </c>
+      <c r="H113" s="46">
+        <f t="shared" si="77"/>
+        <v>3850</v>
+      </c>
+      <c r="I113" s="45">
+        <f t="shared" si="78"/>
+        <v>400</v>
+      </c>
+      <c r="J113" s="45">
+        <f t="shared" si="79"/>
+        <v>100</v>
+      </c>
+      <c r="K113" s="45">
+        <v>0</v>
+      </c>
+      <c r="L113" s="47"/>
+      <c r="M113" s="45"/>
+      <c r="N113" s="44">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="O113" s="45">
+        <f t="shared" si="81"/>
+        <v>1</v>
+      </c>
+      <c r="P113" s="47">
+        <f>IF(D113&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C114" s="61"/>
+      <c r="D114" s="44">
+        <v>15</v>
+      </c>
+      <c r="E114" s="45">
+        <f t="shared" si="75"/>
+        <v>50</v>
+      </c>
+      <c r="F114" s="45">
+        <f t="shared" si="76"/>
+        <v>50</v>
+      </c>
+      <c r="G114" s="45">
+        <v>15</v>
+      </c>
+      <c r="H114" s="46">
+        <f t="shared" si="77"/>
+        <v>3500</v>
+      </c>
+      <c r="I114" s="45">
+        <f t="shared" si="78"/>
+        <v>400</v>
+      </c>
+      <c r="J114" s="45">
+        <f t="shared" si="79"/>
+        <v>150</v>
+      </c>
+      <c r="K114" s="45">
+        <v>0</v>
+      </c>
+      <c r="L114" s="47"/>
+      <c r="M114" s="45"/>
+      <c r="N114" s="44">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="O114" s="45">
+        <f t="shared" si="81"/>
+        <v>1</v>
+      </c>
+      <c r="P114" s="47">
+        <f>IF(D114&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C115" s="61"/>
+      <c r="D115" s="48">
+        <v>20</v>
+      </c>
+      <c r="E115" s="49">
+        <f t="shared" si="75"/>
+        <v>50</v>
+      </c>
+      <c r="F115" s="49">
+        <f t="shared" si="76"/>
+        <v>45</v>
+      </c>
+      <c r="G115" s="49">
+        <v>15</v>
+      </c>
+      <c r="H115" s="50">
+        <f t="shared" si="77"/>
+        <v>3150</v>
+      </c>
+      <c r="I115" s="49">
+        <f t="shared" si="78"/>
+        <v>400</v>
+      </c>
+      <c r="J115" s="49">
+        <f t="shared" si="79"/>
+        <v>200</v>
+      </c>
+      <c r="K115" s="49">
+        <v>0</v>
+      </c>
+      <c r="L115" s="51"/>
+      <c r="M115" s="45"/>
+      <c r="N115" s="48">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="O115" s="49">
+        <f t="shared" si="81"/>
+        <v>1</v>
+      </c>
+      <c r="P115" s="51">
+        <f>IF(D115&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C116" s="61"/>
+      <c r="D116" s="53"/>
+      <c r="E116" s="54"/>
+      <c r="F116" s="54"/>
+      <c r="G116" s="54"/>
+      <c r="H116" s="54"/>
+      <c r="I116" s="54"/>
+      <c r="J116" s="54"/>
+      <c r="K116" s="54"/>
+      <c r="L116" s="54"/>
+      <c r="M116" s="54"/>
+      <c r="N116" s="54"/>
+      <c r="O116" s="54"/>
+      <c r="P116" s="55"/>
+    </row>
+    <row r="117" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C117" s="61"/>
+      <c r="D117" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="E117" s="54"/>
+      <c r="F117" s="54"/>
+      <c r="G117" s="54"/>
+      <c r="H117" s="54"/>
+      <c r="I117" s="54"/>
+      <c r="J117" s="54"/>
+      <c r="K117" s="54"/>
+      <c r="L117" s="54"/>
+      <c r="M117" s="54"/>
+      <c r="N117" s="54"/>
+      <c r="O117" s="54"/>
+      <c r="P117" s="55"/>
+    </row>
+    <row r="118" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C118" s="61"/>
+      <c r="D118" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="E118" s="54">
+        <v>20</v>
+      </c>
+      <c r="F118" s="54"/>
+      <c r="G118" s="54"/>
+      <c r="H118" s="54"/>
+      <c r="I118" s="54"/>
+      <c r="J118" s="54"/>
+      <c r="K118" s="54"/>
+      <c r="L118" s="54"/>
+      <c r="M118" s="54"/>
+      <c r="N118" s="54"/>
+      <c r="O118" s="54"/>
+      <c r="P118" s="55"/>
+    </row>
+    <row r="119" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C119" s="61"/>
+      <c r="D119" s="63" t="s">
+        <v>51</v>
+      </c>
+      <c r="E119" s="64" t="s">
+        <v>66</v>
+      </c>
+      <c r="F119" s="64" t="s">
+        <v>69</v>
+      </c>
+      <c r="G119" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="H119" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="I119" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="J119" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="K119" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="L119" s="66" t="s">
+        <v>100</v>
+      </c>
+      <c r="M119" s="54"/>
+      <c r="N119" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="O119" s="68" t="s">
+        <v>102</v>
+      </c>
+      <c r="P119" s="69" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="120" spans="3:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="C120" s="61"/>
+      <c r="D120" s="44">
+        <v>0</v>
+      </c>
+      <c r="E120" s="45">
+        <f>$K$6</f>
+        <v>50</v>
+      </c>
+      <c r="F120" s="45">
+        <f>E120+G120-D120</f>
+        <v>70</v>
+      </c>
+      <c r="G120" s="45">
+        <v>20</v>
+      </c>
+      <c r="H120" s="46">
+        <f>$E$7*F120</f>
+        <v>4900</v>
+      </c>
+      <c r="I120" s="45">
+        <f>$E$6*IF(F120&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J120" s="45">
+        <f>D120*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K120" s="45">
+        <v>0</v>
+      </c>
+      <c r="L120" s="47"/>
+      <c r="M120" s="45"/>
+      <c r="N120" s="44">
+        <f>IF(F120&lt;=$E$4,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O120" s="45">
+        <f>IF(G120&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P120" s="47">
+        <f>IF(D120&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C121" s="61"/>
+      <c r="D121" s="44">
+        <v>5</v>
+      </c>
+      <c r="E121" s="45">
+        <f t="shared" ref="E121:E124" si="82">$K$6</f>
+        <v>50</v>
+      </c>
+      <c r="F121" s="45">
+        <f t="shared" ref="F121:F124" si="83">E121+G121-D121</f>
+        <v>65</v>
+      </c>
+      <c r="G121" s="45">
+        <v>20</v>
+      </c>
+      <c r="H121" s="46">
+        <f t="shared" ref="H121:H124" si="84">$E$7*F121</f>
+        <v>4550</v>
+      </c>
+      <c r="I121" s="45">
+        <f t="shared" ref="I121:I124" si="85">$E$6*IF(F121&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J121" s="45">
+        <f t="shared" ref="J121:J124" si="86">D121*$E$9</f>
+        <v>50</v>
+      </c>
+      <c r="K121" s="45">
+        <v>0</v>
+      </c>
+      <c r="L121" s="47"/>
+      <c r="M121" s="45"/>
+      <c r="N121" s="44">
+        <f t="shared" ref="N121:N124" si="87">IF(F121&lt;=$E$4,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O121" s="45">
+        <f t="shared" ref="O121:O124" si="88">IF(G121&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P121" s="47">
+        <f>IF(D121&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C122" s="61"/>
+      <c r="D122" s="44">
+        <v>10</v>
+      </c>
+      <c r="E122" s="45">
+        <f t="shared" si="82"/>
+        <v>50</v>
+      </c>
+      <c r="F122" s="45">
+        <f t="shared" si="83"/>
+        <v>60</v>
+      </c>
+      <c r="G122" s="45">
+        <v>20</v>
+      </c>
+      <c r="H122" s="46">
+        <f t="shared" si="84"/>
+        <v>4200</v>
+      </c>
+      <c r="I122" s="45">
+        <f t="shared" si="85"/>
+        <v>400</v>
+      </c>
+      <c r="J122" s="45">
+        <f t="shared" si="86"/>
+        <v>100</v>
+      </c>
+      <c r="K122" s="45">
+        <v>0</v>
+      </c>
+      <c r="L122" s="47"/>
+      <c r="M122" s="45"/>
+      <c r="N122" s="44">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="O122" s="45">
+        <f t="shared" si="88"/>
+        <v>1</v>
+      </c>
+      <c r="P122" s="47">
+        <f>IF(D122&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C123" s="61"/>
+      <c r="D123" s="44">
+        <v>15</v>
+      </c>
+      <c r="E123" s="45">
+        <f t="shared" si="82"/>
+        <v>50</v>
+      </c>
+      <c r="F123" s="45">
+        <f t="shared" si="83"/>
+        <v>55</v>
+      </c>
+      <c r="G123" s="45">
+        <v>20</v>
+      </c>
+      <c r="H123" s="46">
+        <f t="shared" si="84"/>
+        <v>3850</v>
+      </c>
+      <c r="I123" s="45">
+        <f t="shared" si="85"/>
+        <v>400</v>
+      </c>
+      <c r="J123" s="45">
+        <f t="shared" si="86"/>
+        <v>150</v>
+      </c>
+      <c r="K123" s="45">
+        <v>0</v>
+      </c>
+      <c r="L123" s="47"/>
+      <c r="M123" s="45"/>
+      <c r="N123" s="44">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="O123" s="45">
+        <f t="shared" si="88"/>
+        <v>1</v>
+      </c>
+      <c r="P123" s="47">
+        <f>IF(D123&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C124" s="61"/>
+      <c r="D124" s="48">
+        <v>20</v>
+      </c>
+      <c r="E124" s="49">
+        <f t="shared" si="82"/>
+        <v>50</v>
+      </c>
+      <c r="F124" s="49">
+        <f t="shared" si="83"/>
+        <v>50</v>
+      </c>
+      <c r="G124" s="49">
+        <v>20</v>
+      </c>
+      <c r="H124" s="50">
+        <f t="shared" si="84"/>
+        <v>3500</v>
+      </c>
+      <c r="I124" s="49">
+        <f t="shared" si="85"/>
+        <v>400</v>
+      </c>
+      <c r="J124" s="49">
+        <f t="shared" si="86"/>
+        <v>200</v>
+      </c>
+      <c r="K124" s="49">
+        <v>0</v>
+      </c>
+      <c r="L124" s="51"/>
+      <c r="M124" s="45"/>
+      <c r="N124" s="48">
+        <f t="shared" si="87"/>
+        <v>0</v>
+      </c>
+      <c r="O124" s="49">
+        <f t="shared" si="88"/>
+        <v>1</v>
+      </c>
+      <c r="P124" s="51">
+        <f>IF(D124&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C125" s="61"/>
+      <c r="D125" s="53"/>
+      <c r="E125" s="54"/>
+      <c r="F125" s="54"/>
+      <c r="G125" s="54"/>
+      <c r="H125" s="54"/>
+      <c r="I125" s="54"/>
+      <c r="J125" s="54"/>
+      <c r="K125" s="54"/>
+      <c r="L125" s="54"/>
+      <c r="M125" s="54"/>
+      <c r="N125" s="54"/>
+      <c r="O125" s="54"/>
+      <c r="P125" s="55"/>
+    </row>
+    <row r="126" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C126" s="61"/>
+      <c r="D126" s="70" t="s">
+        <v>105</v>
+      </c>
+      <c r="E126" s="71"/>
+      <c r="F126" s="54"/>
+      <c r="G126" s="54"/>
+      <c r="H126" s="54"/>
+      <c r="I126" s="54"/>
+      <c r="J126" s="54"/>
+      <c r="K126" s="54"/>
+      <c r="L126" s="54"/>
+      <c r="M126" s="54"/>
+      <c r="N126" s="54"/>
+      <c r="O126" s="54"/>
+      <c r="P126" s="55"/>
+    </row>
+    <row r="127" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C127" s="61"/>
+      <c r="D127" s="63" t="s">
+        <v>50</v>
+      </c>
+      <c r="E127" s="66" t="s">
+        <v>106</v>
+      </c>
+      <c r="F127" s="54"/>
+      <c r="G127" s="54"/>
+      <c r="H127" s="54"/>
+      <c r="I127" s="54"/>
+      <c r="J127" s="54"/>
+      <c r="K127" s="54"/>
+      <c r="L127" s="54"/>
+      <c r="M127" s="54"/>
+      <c r="N127" s="54"/>
+      <c r="O127" s="54"/>
+      <c r="P127" s="55"/>
+    </row>
+    <row r="128" spans="3:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="C128" s="61"/>
+      <c r="D128" s="44">
+        <v>0</v>
+      </c>
+      <c r="E128" s="47">
+        <f>MIN(L84,L93,L102,L111,L120)</f>
+        <v>0</v>
+      </c>
+      <c r="F128" s="54"/>
+      <c r="G128" s="54"/>
+      <c r="H128" s="54"/>
+      <c r="I128" s="54"/>
+      <c r="J128" s="54"/>
+      <c r="K128" s="54"/>
+      <c r="L128" s="54"/>
+      <c r="M128" s="54"/>
+      <c r="N128" s="54"/>
+      <c r="O128" s="54"/>
+      <c r="P128" s="55"/>
+    </row>
+    <row r="129" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C129" s="61"/>
+      <c r="D129" s="44">
+        <v>5</v>
+      </c>
+      <c r="E129" s="47">
+        <f t="shared" ref="E129:E131" si="89">MIN(L85,L94,L103,L112,L121)</f>
+        <v>0</v>
+      </c>
+      <c r="F129" s="54"/>
+      <c r="G129" s="54"/>
+      <c r="H129" s="54"/>
+      <c r="I129" s="54"/>
+      <c r="J129" s="54"/>
+      <c r="K129" s="54"/>
+      <c r="L129" s="54"/>
+      <c r="M129" s="54"/>
+      <c r="N129" s="54"/>
+      <c r="O129" s="54"/>
+      <c r="P129" s="55"/>
+    </row>
+    <row r="130" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C130" s="61"/>
+      <c r="D130" s="80">
+        <v>10</v>
+      </c>
+      <c r="E130" s="81">
+        <f>MIN(L86,L95,L104,L113,L122)</f>
+        <v>6000</v>
+      </c>
+      <c r="F130" s="54"/>
+      <c r="G130" s="54"/>
+      <c r="H130" s="54"/>
+      <c r="I130" s="54"/>
+      <c r="J130" s="54"/>
+      <c r="K130" s="54"/>
+      <c r="L130" s="54"/>
+      <c r="M130" s="54"/>
+      <c r="N130" s="54"/>
+      <c r="O130" s="54"/>
+      <c r="P130" s="55"/>
+    </row>
+    <row r="131" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C131" s="61"/>
+      <c r="D131" s="53">
+        <v>15</v>
+      </c>
+      <c r="E131" s="55">
+        <f t="shared" si="89"/>
+        <v>5700</v>
+      </c>
+      <c r="F131" s="54"/>
+      <c r="G131" s="54"/>
+      <c r="H131" s="54"/>
+      <c r="I131" s="54"/>
+      <c r="J131" s="54"/>
+      <c r="K131" s="54"/>
+      <c r="L131" s="54"/>
+      <c r="M131" s="54"/>
+      <c r="N131" s="54"/>
+      <c r="O131" s="54"/>
+      <c r="P131" s="55"/>
+    </row>
+    <row r="132" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C132" s="61"/>
+      <c r="D132" s="78">
+        <v>20</v>
+      </c>
+      <c r="E132" s="79">
+        <f>MIN(L88,L97,L106,L115,L124)</f>
+        <v>5300</v>
+      </c>
+      <c r="F132" s="57"/>
+      <c r="G132" s="57"/>
+      <c r="H132" s="57"/>
+      <c r="I132" s="57"/>
+      <c r="J132" s="57"/>
+      <c r="K132" s="57"/>
+      <c r="L132" s="57"/>
+      <c r="M132" s="57"/>
+      <c r="N132" s="57"/>
+      <c r="O132" s="57"/>
+      <c r="P132" s="58"/>
+    </row>
+    <row r="133" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C133" s="61"/>
+      <c r="D133" s="61"/>
+      <c r="E133" s="61"/>
+      <c r="F133" s="61"/>
+      <c r="G133" s="61"/>
+      <c r="H133" s="61"/>
+      <c r="I133" s="61"/>
+      <c r="J133" s="61"/>
+      <c r="K133" s="61"/>
+      <c r="L133" s="61"/>
+      <c r="M133" s="61"/>
+      <c r="N133" s="61"/>
+      <c r="O133" s="61"/>
+      <c r="P133" s="61"/>
+    </row>
+    <row r="134" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C134" s="61"/>
+      <c r="D134" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="E134" s="32"/>
+      <c r="F134" s="32"/>
+      <c r="G134" s="32"/>
+      <c r="H134" s="32"/>
+      <c r="I134" s="32"/>
+      <c r="J134" s="32"/>
+      <c r="K134" s="32"/>
+      <c r="L134" s="32"/>
+      <c r="M134" s="32"/>
+      <c r="N134" s="32"/>
+      <c r="O134" s="32"/>
+      <c r="P134" s="24"/>
+    </row>
+    <row r="135" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C135" s="61"/>
+      <c r="D135" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="E135" s="54"/>
+      <c r="F135" s="54"/>
+      <c r="G135" s="54"/>
+      <c r="H135" s="54"/>
+      <c r="I135" s="54"/>
+      <c r="J135" s="54"/>
+      <c r="K135" s="54"/>
+      <c r="L135" s="54"/>
+      <c r="M135" s="54"/>
+      <c r="N135" s="54"/>
+      <c r="O135" s="54"/>
+      <c r="P135" s="55"/>
+    </row>
+    <row r="136" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C136" s="61"/>
+      <c r="D136" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="E136" s="54">
+        <v>10</v>
+      </c>
+      <c r="F136" s="54"/>
+      <c r="G136" s="54"/>
+      <c r="H136" s="54"/>
+      <c r="I136" s="54"/>
+      <c r="J136" s="54"/>
+      <c r="K136" s="54"/>
+      <c r="L136" s="54"/>
+      <c r="M136" s="54"/>
+      <c r="N136" s="54"/>
+      <c r="O136" s="54"/>
+      <c r="P136" s="55"/>
+    </row>
+    <row r="137" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C137" s="61"/>
+      <c r="D137" s="63" t="s">
+        <v>51</v>
+      </c>
+      <c r="E137" s="64" t="s">
+        <v>66</v>
+      </c>
+      <c r="F137" s="64" t="s">
+        <v>69</v>
+      </c>
+      <c r="G137" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="H137" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="I137" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="J137" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="K137" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="L137" s="66" t="s">
+        <v>100</v>
+      </c>
+      <c r="M137" s="54"/>
+      <c r="N137" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="O137" s="68" t="s">
+        <v>102</v>
+      </c>
+      <c r="P137" s="69" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="138" spans="3:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="C138" s="61"/>
+      <c r="D138" s="53">
+        <v>0</v>
+      </c>
+      <c r="E138" s="54">
+        <f>$K$7</f>
+        <v>10</v>
+      </c>
+      <c r="F138" s="54">
+        <f>E138+G138-D138</f>
+        <v>20</v>
+      </c>
+      <c r="G138" s="54">
+        <v>10</v>
+      </c>
+      <c r="H138" s="62">
+        <f>$E$7*F138</f>
+        <v>1400</v>
+      </c>
+      <c r="I138" s="54">
+        <f>$E$6*IF(F138&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J138" s="54">
+        <f>D138*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K138" s="54">
+        <v>0</v>
+      </c>
+      <c r="L138" s="55">
+        <f>SUM(H138:K138)+$E$130</f>
+        <v>7800</v>
+      </c>
+      <c r="M138" s="54"/>
+      <c r="N138" s="53">
+        <f>IF(F138&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O138" s="54">
+        <f>IF(G138&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P138" s="55">
+        <f>IF(D138&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C139" s="61"/>
+      <c r="D139" s="53">
+        <v>5</v>
+      </c>
+      <c r="E139" s="54">
+        <f t="shared" ref="E139:E142" si="90">$K$7</f>
+        <v>10</v>
+      </c>
+      <c r="F139" s="54">
+        <f t="shared" ref="F139:F142" si="91">E139+G139-D139</f>
+        <v>15</v>
+      </c>
+      <c r="G139" s="54">
+        <v>10</v>
+      </c>
+      <c r="H139" s="62">
+        <f t="shared" ref="H139:H142" si="92">$E$7*F139</f>
+        <v>1050</v>
+      </c>
+      <c r="I139" s="54">
+        <f t="shared" ref="I139:I142" si="93">$E$6*IF(F139&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J139" s="54">
+        <f t="shared" ref="J139:J142" si="94">D139*$E$9</f>
+        <v>50</v>
+      </c>
+      <c r="K139" s="54">
+        <v>0</v>
+      </c>
+      <c r="L139" s="55">
+        <f t="shared" ref="L139:L142" si="95">SUM(H139:K139)+$E$130</f>
+        <v>7500</v>
+      </c>
+      <c r="M139" s="54"/>
+      <c r="N139" s="53">
+        <f t="shared" ref="N139:N142" si="96">IF(F139&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O139" s="54">
+        <f t="shared" ref="O139:O142" si="97">IF(G139&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P139" s="55">
+        <f>IF(D139&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C140" s="61"/>
+      <c r="D140" s="53">
+        <v>10</v>
+      </c>
+      <c r="E140" s="54">
+        <f t="shared" si="90"/>
+        <v>10</v>
+      </c>
+      <c r="F140" s="54">
+        <f t="shared" si="91"/>
+        <v>10</v>
+      </c>
+      <c r="G140" s="54">
+        <v>10</v>
+      </c>
+      <c r="H140" s="62">
+        <f t="shared" si="92"/>
+        <v>700</v>
+      </c>
+      <c r="I140" s="54">
+        <f t="shared" si="93"/>
+        <v>400</v>
+      </c>
+      <c r="J140" s="54">
+        <f t="shared" si="94"/>
+        <v>100</v>
+      </c>
+      <c r="K140" s="54">
+        <v>0</v>
+      </c>
+      <c r="L140" s="55">
+        <f t="shared" si="95"/>
+        <v>7200</v>
+      </c>
+      <c r="M140" s="54"/>
+      <c r="N140" s="53">
+        <f t="shared" si="96"/>
+        <v>1</v>
+      </c>
+      <c r="O140" s="54">
+        <f t="shared" si="97"/>
+        <v>1</v>
+      </c>
+      <c r="P140" s="55">
+        <f>IF(D140&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C141" s="61"/>
+      <c r="D141" s="53">
+        <v>15</v>
+      </c>
+      <c r="E141" s="54">
+        <f t="shared" si="90"/>
+        <v>10</v>
+      </c>
+      <c r="F141" s="54">
+        <f t="shared" si="91"/>
+        <v>5</v>
+      </c>
+      <c r="G141" s="54">
+        <v>10</v>
+      </c>
+      <c r="H141" s="62">
+        <f t="shared" si="92"/>
+        <v>350</v>
+      </c>
+      <c r="I141" s="54">
+        <f t="shared" si="93"/>
+        <v>400</v>
+      </c>
+      <c r="J141" s="54">
+        <f t="shared" si="94"/>
+        <v>150</v>
+      </c>
+      <c r="K141" s="54">
+        <v>0</v>
+      </c>
+      <c r="L141" s="55">
+        <f t="shared" si="95"/>
+        <v>6900</v>
+      </c>
+      <c r="M141" s="54"/>
+      <c r="N141" s="53">
+        <f t="shared" si="96"/>
+        <v>1</v>
+      </c>
+      <c r="O141" s="54">
+        <f t="shared" si="97"/>
+        <v>1</v>
+      </c>
+      <c r="P141" s="55">
+        <f>IF(D141&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C142" s="61"/>
+      <c r="D142" s="56">
+        <v>20</v>
+      </c>
+      <c r="E142" s="57">
+        <f t="shared" si="90"/>
+        <v>10</v>
+      </c>
+      <c r="F142" s="76">
+        <f t="shared" si="91"/>
+        <v>0</v>
+      </c>
+      <c r="G142" s="57">
+        <v>10</v>
+      </c>
+      <c r="H142" s="59">
+        <f t="shared" si="92"/>
+        <v>0</v>
+      </c>
+      <c r="I142" s="57">
+        <f t="shared" si="93"/>
+        <v>0</v>
+      </c>
+      <c r="J142" s="57">
+        <f t="shared" si="94"/>
+        <v>200</v>
+      </c>
+      <c r="K142" s="57">
+        <v>0</v>
+      </c>
+      <c r="L142" s="34">
+        <f>SUM(H142:K142)+$E$130</f>
+        <v>6200</v>
+      </c>
+      <c r="M142" s="54"/>
+      <c r="N142" s="56">
+        <f t="shared" si="96"/>
+        <v>1</v>
+      </c>
+      <c r="O142" s="57">
+        <f t="shared" si="97"/>
+        <v>1</v>
+      </c>
+      <c r="P142" s="58">
+        <f>IF(D142&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C143" s="61"/>
+      <c r="D143" s="53"/>
+      <c r="E143" s="54"/>
+      <c r="F143" s="54"/>
+      <c r="G143" s="54"/>
+      <c r="H143" s="54"/>
+      <c r="I143" s="54"/>
+      <c r="J143" s="54"/>
+      <c r="K143" s="54"/>
+      <c r="L143" s="54"/>
+      <c r="M143" s="54"/>
+      <c r="N143" s="54"/>
+      <c r="O143" s="54"/>
+      <c r="P143" s="55"/>
+    </row>
+    <row r="144" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C144" s="61"/>
+      <c r="D144" s="53" t="s">
+        <v>76</v>
+      </c>
+      <c r="E144" s="54"/>
+      <c r="F144" s="54"/>
+      <c r="G144" s="54"/>
+      <c r="H144" s="54"/>
+      <c r="I144" s="54"/>
+      <c r="J144" s="54"/>
+      <c r="K144" s="54"/>
+      <c r="L144" s="54"/>
+      <c r="M144" s="54"/>
+      <c r="N144" s="54"/>
+      <c r="O144" s="54"/>
+      <c r="P144" s="55"/>
+    </row>
+    <row r="145" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C145" s="61"/>
+      <c r="D145" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="E145" s="54">
+        <v>15</v>
+      </c>
+      <c r="F145" s="54"/>
+      <c r="G145" s="54"/>
+      <c r="H145" s="54"/>
+      <c r="I145" s="54"/>
+      <c r="J145" s="54"/>
+      <c r="K145" s="54"/>
+      <c r="L145" s="54"/>
+      <c r="M145" s="54"/>
+      <c r="N145" s="54"/>
+      <c r="O145" s="54"/>
+      <c r="P145" s="55"/>
+    </row>
+    <row r="146" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C146" s="61"/>
+      <c r="D146" s="63" t="s">
+        <v>51</v>
+      </c>
+      <c r="E146" s="64" t="s">
+        <v>66</v>
+      </c>
+      <c r="F146" s="64" t="s">
+        <v>69</v>
+      </c>
+      <c r="G146" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="H146" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="I146" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="J146" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="K146" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="L146" s="66" t="s">
+        <v>100</v>
+      </c>
+      <c r="M146" s="54"/>
+      <c r="N146" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="O146" s="68" t="s">
+        <v>102</v>
+      </c>
+      <c r="P146" s="69" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="147" spans="3:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="C147" s="61"/>
+      <c r="D147" s="53">
+        <v>0</v>
+      </c>
+      <c r="E147" s="54">
+        <f>$K$7</f>
+        <v>10</v>
+      </c>
+      <c r="F147" s="54">
+        <f>E147+G147-D147</f>
+        <v>25</v>
+      </c>
+      <c r="G147" s="54">
+        <v>15</v>
+      </c>
+      <c r="H147" s="62">
+        <f>$E$7*F147</f>
+        <v>1750</v>
+      </c>
+      <c r="I147" s="54">
+        <f>$E$6*IF(F147&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J147" s="54">
+        <f>D147*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K147" s="54">
+        <v>0</v>
+      </c>
+      <c r="L147" s="55">
+        <f>SUM(H147:K147)+$E$131</f>
+        <v>7850</v>
+      </c>
+      <c r="M147" s="54"/>
+      <c r="N147" s="53">
+        <f>IF(F147&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O147" s="54">
+        <f>IF(G147&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P147" s="55">
+        <f>IF(D147&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C148" s="61"/>
+      <c r="D148" s="53">
+        <v>5</v>
+      </c>
+      <c r="E148" s="54">
+        <f t="shared" ref="E148:E151" si="98">$K$7</f>
+        <v>10</v>
+      </c>
+      <c r="F148" s="54">
+        <f t="shared" ref="F148:F151" si="99">E148+G148-D148</f>
+        <v>20</v>
+      </c>
+      <c r="G148" s="54">
+        <v>15</v>
+      </c>
+      <c r="H148" s="62">
+        <f t="shared" ref="H148:H151" si="100">$E$7*F148</f>
+        <v>1400</v>
+      </c>
+      <c r="I148" s="54">
+        <f t="shared" ref="I148:I151" si="101">$E$6*IF(F148&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J148" s="54">
+        <f t="shared" ref="J148:J151" si="102">D148*$E$9</f>
+        <v>50</v>
+      </c>
+      <c r="K148" s="54">
+        <v>0</v>
+      </c>
+      <c r="L148" s="55">
+        <f t="shared" ref="L148:L151" si="103">SUM(H148:K148)+$E$131</f>
+        <v>7550</v>
+      </c>
+      <c r="M148" s="54"/>
+      <c r="N148" s="53">
+        <f t="shared" ref="N148:N151" si="104">IF(F148&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O148" s="54">
+        <f t="shared" ref="O148:O151" si="105">IF(G148&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P148" s="55">
+        <f>IF(D148&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C149" s="61"/>
+      <c r="D149" s="53">
+        <v>10</v>
+      </c>
+      <c r="E149" s="54">
+        <f t="shared" si="98"/>
+        <v>10</v>
+      </c>
+      <c r="F149" s="54">
+        <f t="shared" si="99"/>
+        <v>15</v>
+      </c>
+      <c r="G149" s="54">
+        <v>15</v>
+      </c>
+      <c r="H149" s="62">
+        <f t="shared" si="100"/>
+        <v>1050</v>
+      </c>
+      <c r="I149" s="54">
+        <f t="shared" si="101"/>
+        <v>400</v>
+      </c>
+      <c r="J149" s="54">
+        <f t="shared" si="102"/>
+        <v>100</v>
+      </c>
+      <c r="K149" s="54">
+        <v>0</v>
+      </c>
+      <c r="L149" s="55">
+        <f t="shared" si="103"/>
+        <v>7250</v>
+      </c>
+      <c r="M149" s="54"/>
+      <c r="N149" s="53">
+        <f t="shared" si="104"/>
+        <v>1</v>
+      </c>
+      <c r="O149" s="54">
+        <f t="shared" si="105"/>
+        <v>1</v>
+      </c>
+      <c r="P149" s="55">
+        <f>IF(D149&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C150" s="61"/>
+      <c r="D150" s="53">
+        <v>15</v>
+      </c>
+      <c r="E150" s="54">
+        <f t="shared" si="98"/>
+        <v>10</v>
+      </c>
+      <c r="F150" s="54">
+        <f t="shared" si="99"/>
+        <v>10</v>
+      </c>
+      <c r="G150" s="54">
+        <v>15</v>
+      </c>
+      <c r="H150" s="62">
+        <f t="shared" si="100"/>
+        <v>700</v>
+      </c>
+      <c r="I150" s="54">
+        <f t="shared" si="101"/>
+        <v>400</v>
+      </c>
+      <c r="J150" s="54">
+        <f t="shared" si="102"/>
+        <v>150</v>
+      </c>
+      <c r="K150" s="54">
+        <v>0</v>
+      </c>
+      <c r="L150" s="55">
+        <f t="shared" si="103"/>
+        <v>6950</v>
+      </c>
+      <c r="M150" s="54"/>
+      <c r="N150" s="53">
+        <f t="shared" si="104"/>
+        <v>1</v>
+      </c>
+      <c r="O150" s="54">
+        <f t="shared" si="105"/>
+        <v>1</v>
+      </c>
+      <c r="P150" s="55">
+        <f>IF(D150&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C151" s="61"/>
+      <c r="D151" s="56">
+        <v>20</v>
+      </c>
+      <c r="E151" s="57">
+        <f t="shared" si="98"/>
+        <v>10</v>
+      </c>
+      <c r="F151" s="57">
+        <f t="shared" si="99"/>
+        <v>5</v>
+      </c>
+      <c r="G151" s="57">
+        <v>15</v>
+      </c>
+      <c r="H151" s="59">
+        <f t="shared" si="100"/>
+        <v>350</v>
+      </c>
+      <c r="I151" s="57">
+        <f t="shared" si="101"/>
+        <v>400</v>
+      </c>
+      <c r="J151" s="57">
+        <f t="shared" si="102"/>
+        <v>200</v>
+      </c>
+      <c r="K151" s="57">
+        <v>0</v>
+      </c>
+      <c r="L151" s="58">
+        <f t="shared" si="103"/>
+        <v>6650</v>
+      </c>
+      <c r="M151" s="54"/>
+      <c r="N151" s="56">
+        <f t="shared" si="104"/>
+        <v>1</v>
+      </c>
+      <c r="O151" s="57">
+        <f t="shared" si="105"/>
+        <v>1</v>
+      </c>
+      <c r="P151" s="58">
+        <f>IF(D151&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C152" s="61"/>
+      <c r="D152" s="53"/>
+      <c r="E152" s="54"/>
+      <c r="F152" s="54"/>
+      <c r="G152" s="54"/>
+      <c r="H152" s="54"/>
+      <c r="I152" s="54"/>
+      <c r="J152" s="54"/>
+      <c r="K152" s="54"/>
+      <c r="L152" s="54"/>
+      <c r="M152" s="54"/>
+      <c r="N152" s="54"/>
+      <c r="O152" s="54"/>
+      <c r="P152" s="55"/>
+    </row>
+    <row r="153" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C153" s="61"/>
+      <c r="D153" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="E153" s="54"/>
+      <c r="F153" s="54"/>
+      <c r="G153" s="54"/>
+      <c r="H153" s="54"/>
+      <c r="I153" s="54"/>
+      <c r="J153" s="54"/>
+      <c r="K153" s="54"/>
+      <c r="L153" s="54"/>
+      <c r="M153" s="54"/>
+      <c r="N153" s="54"/>
+      <c r="O153" s="54"/>
+      <c r="P153" s="55"/>
+    </row>
+    <row r="154" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C154" s="61"/>
+      <c r="D154" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="E154" s="54">
+        <v>20</v>
+      </c>
+      <c r="F154" s="54"/>
+      <c r="G154" s="54"/>
+      <c r="H154" s="54"/>
+      <c r="I154" s="54"/>
+      <c r="J154" s="54"/>
+      <c r="K154" s="54"/>
+      <c r="L154" s="54"/>
+      <c r="M154" s="54"/>
+      <c r="N154" s="54"/>
+      <c r="O154" s="54"/>
+      <c r="P154" s="55"/>
+    </row>
+    <row r="155" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C155" s="61"/>
+      <c r="D155" s="63" t="s">
+        <v>51</v>
+      </c>
+      <c r="E155" s="64" t="s">
+        <v>66</v>
+      </c>
+      <c r="F155" s="64" t="s">
+        <v>69</v>
+      </c>
+      <c r="G155" s="64" t="s">
+        <v>50</v>
+      </c>
+      <c r="H155" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="I155" s="64" t="s">
+        <v>71</v>
+      </c>
+      <c r="J155" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="K155" s="64" t="s">
+        <v>63</v>
+      </c>
+      <c r="L155" s="66" t="s">
+        <v>100</v>
+      </c>
+      <c r="M155" s="54"/>
+      <c r="N155" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="O155" s="68" t="s">
+        <v>102</v>
+      </c>
+      <c r="P155" s="69" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="156" spans="3:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="C156" s="61"/>
+      <c r="D156" s="53">
+        <v>0</v>
+      </c>
+      <c r="E156" s="54">
+        <f>$K$7</f>
+        <v>10</v>
+      </c>
+      <c r="F156" s="54">
+        <f>E156+G156-D156</f>
+        <v>30</v>
+      </c>
+      <c r="G156" s="54">
+        <v>20</v>
+      </c>
+      <c r="H156" s="62">
+        <f>$E$7*F156</f>
+        <v>2100</v>
+      </c>
+      <c r="I156" s="54">
+        <f>$E$6*IF(F156&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J156" s="54">
+        <f>D156*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K156" s="54">
+        <v>0</v>
+      </c>
+      <c r="L156" s="55">
+        <f>SUM(H156:K156)+$E$132</f>
+        <v>7800</v>
+      </c>
+      <c r="M156" s="54"/>
+      <c r="N156" s="53">
+        <f>IF(F156&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O156" s="54">
+        <f>IF(G156&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P156" s="55">
+        <f>IF(D156&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C157" s="61"/>
+      <c r="D157" s="53">
+        <v>5</v>
+      </c>
+      <c r="E157" s="54">
+        <f t="shared" ref="E157:E160" si="106">$K$7</f>
+        <v>10</v>
+      </c>
+      <c r="F157" s="54">
+        <f t="shared" ref="F157:F160" si="107">E157+G157-D157</f>
+        <v>25</v>
+      </c>
+      <c r="G157" s="54">
+        <v>20</v>
+      </c>
+      <c r="H157" s="62">
+        <f t="shared" ref="H157:H160" si="108">$E$7*F157</f>
+        <v>1750</v>
+      </c>
+      <c r="I157" s="54">
+        <f t="shared" ref="I157:I160" si="109">$E$6*IF(F157&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J157" s="54">
+        <f t="shared" ref="J157:J160" si="110">D157*$E$9</f>
+        <v>50</v>
+      </c>
+      <c r="K157" s="54">
+        <v>0</v>
+      </c>
+      <c r="L157" s="55">
+        <f t="shared" ref="L157:L160" si="111">SUM(H157:K157)+$E$132</f>
+        <v>7500</v>
+      </c>
+      <c r="M157" s="54"/>
+      <c r="N157" s="53">
+        <f t="shared" ref="N157:N160" si="112">IF(F157&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O157" s="54">
+        <f t="shared" ref="O157:O160" si="113">IF(G157&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P157" s="55">
+        <f>IF(D157&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C158" s="61"/>
+      <c r="D158" s="53">
+        <v>10</v>
+      </c>
+      <c r="E158" s="54">
+        <f t="shared" si="106"/>
+        <v>10</v>
+      </c>
+      <c r="F158" s="54">
+        <f t="shared" si="107"/>
+        <v>20</v>
+      </c>
+      <c r="G158" s="54">
+        <v>20</v>
+      </c>
+      <c r="H158" s="62">
+        <f t="shared" si="108"/>
+        <v>1400</v>
+      </c>
+      <c r="I158" s="54">
+        <f t="shared" si="109"/>
+        <v>400</v>
+      </c>
+      <c r="J158" s="54">
+        <f t="shared" si="110"/>
+        <v>100</v>
+      </c>
+      <c r="K158" s="54">
+        <v>0</v>
+      </c>
+      <c r="L158" s="55">
+        <f t="shared" si="111"/>
+        <v>7200</v>
+      </c>
+      <c r="M158" s="54"/>
+      <c r="N158" s="53">
+        <f t="shared" si="112"/>
+        <v>1</v>
+      </c>
+      <c r="O158" s="54">
+        <f t="shared" si="113"/>
+        <v>1</v>
+      </c>
+      <c r="P158" s="55">
+        <f>IF(D158&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C159" s="61"/>
+      <c r="D159" s="53">
+        <v>15</v>
+      </c>
+      <c r="E159" s="54">
+        <f t="shared" si="106"/>
+        <v>10</v>
+      </c>
+      <c r="F159" s="54">
+        <f t="shared" si="107"/>
+        <v>15</v>
+      </c>
+      <c r="G159" s="54">
+        <v>20</v>
+      </c>
+      <c r="H159" s="62">
+        <f t="shared" si="108"/>
+        <v>1050</v>
+      </c>
+      <c r="I159" s="54">
+        <f t="shared" si="109"/>
+        <v>400</v>
+      </c>
+      <c r="J159" s="54">
+        <f t="shared" si="110"/>
+        <v>150</v>
+      </c>
+      <c r="K159" s="54">
+        <v>0</v>
+      </c>
+      <c r="L159" s="55">
+        <f t="shared" si="111"/>
+        <v>6900</v>
+      </c>
+      <c r="M159" s="54"/>
+      <c r="N159" s="53">
+        <f t="shared" si="112"/>
+        <v>1</v>
+      </c>
+      <c r="O159" s="54">
+        <f t="shared" si="113"/>
+        <v>1</v>
+      </c>
+      <c r="P159" s="55">
+        <f>IF(D159&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C160" s="61"/>
+      <c r="D160" s="56">
+        <v>20</v>
+      </c>
+      <c r="E160" s="57">
+        <f t="shared" si="106"/>
+        <v>10</v>
+      </c>
+      <c r="F160" s="57">
+        <f t="shared" si="107"/>
+        <v>10</v>
+      </c>
+      <c r="G160" s="57">
+        <v>20</v>
+      </c>
+      <c r="H160" s="59">
+        <f t="shared" si="108"/>
+        <v>700</v>
+      </c>
+      <c r="I160" s="57">
+        <f t="shared" si="109"/>
+        <v>400</v>
+      </c>
+      <c r="J160" s="57">
+        <f t="shared" si="110"/>
+        <v>200</v>
+      </c>
+      <c r="K160" s="57">
+        <v>0</v>
+      </c>
+      <c r="L160" s="58">
+        <f t="shared" si="111"/>
+        <v>6600</v>
+      </c>
+      <c r="M160" s="54"/>
+      <c r="N160" s="56">
+        <f t="shared" si="112"/>
+        <v>1</v>
+      </c>
+      <c r="O160" s="57">
+        <f t="shared" si="113"/>
+        <v>1</v>
+      </c>
+      <c r="P160" s="58">
+        <f>IF(D160&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C161" s="61"/>
+      <c r="D161" s="53"/>
+      <c r="E161" s="54"/>
+      <c r="F161" s="54"/>
+      <c r="G161" s="54"/>
+      <c r="H161" s="54"/>
+      <c r="I161" s="54"/>
+      <c r="J161" s="54"/>
+      <c r="K161" s="54"/>
+      <c r="L161" s="54"/>
+      <c r="M161" s="54"/>
+      <c r="N161" s="54"/>
+      <c r="O161" s="54"/>
+      <c r="P161" s="55"/>
+    </row>
+    <row r="162" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C162" s="61"/>
+      <c r="D162" s="70" t="s">
+        <v>105</v>
+      </c>
+      <c r="E162" s="71"/>
+      <c r="F162" s="54"/>
+      <c r="G162" s="54"/>
+      <c r="H162" s="54"/>
+      <c r="I162" s="54"/>
+      <c r="J162" s="54"/>
+      <c r="K162" s="54"/>
+      <c r="L162" s="54"/>
+      <c r="M162" s="54"/>
+      <c r="N162" s="54"/>
+      <c r="O162" s="54"/>
+      <c r="P162" s="55"/>
+    </row>
+    <row r="163" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C163" s="61"/>
+      <c r="D163" s="63" t="s">
+        <v>50</v>
+      </c>
+      <c r="E163" s="66" t="s">
+        <v>106</v>
+      </c>
+      <c r="F163" s="54"/>
+      <c r="G163" s="54"/>
+      <c r="H163" s="54"/>
+      <c r="I163" s="54"/>
+      <c r="J163" s="54"/>
+      <c r="K163" s="54"/>
+      <c r="L163" s="54"/>
+      <c r="M163" s="54"/>
+      <c r="N163" s="54"/>
+      <c r="O163" s="54"/>
+      <c r="P163" s="55"/>
+    </row>
+    <row r="164" spans="3:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="C164" s="61"/>
+      <c r="D164" s="53">
+        <v>0</v>
+      </c>
+      <c r="E164" s="55">
+        <f>MIN(L138,L147,L156)</f>
+        <v>7800</v>
+      </c>
+      <c r="F164" s="54"/>
+      <c r="G164" s="54"/>
+      <c r="H164" s="54"/>
+      <c r="I164" s="54"/>
+      <c r="J164" s="54"/>
+      <c r="K164" s="54"/>
+      <c r="L164" s="54"/>
+      <c r="M164" s="54"/>
+      <c r="N164" s="54"/>
+      <c r="O164" s="54"/>
+      <c r="P164" s="55"/>
+    </row>
+    <row r="165" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C165" s="61"/>
+      <c r="D165" s="53">
+        <v>5</v>
+      </c>
+      <c r="E165" s="55">
+        <f t="shared" ref="E165:E168" si="114">MIN(L139,L148,L157)</f>
+        <v>7500</v>
+      </c>
+      <c r="F165" s="54"/>
+      <c r="G165" s="54"/>
+      <c r="H165" s="54"/>
+      <c r="I165" s="54"/>
+      <c r="J165" s="54"/>
+      <c r="K165" s="54"/>
+      <c r="L165" s="54"/>
+      <c r="M165" s="54"/>
+      <c r="N165" s="54"/>
+      <c r="O165" s="54"/>
+      <c r="P165" s="55"/>
+    </row>
+    <row r="166" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C166" s="61"/>
+      <c r="D166" s="53">
+        <v>10</v>
+      </c>
+      <c r="E166" s="55">
+        <f t="shared" si="114"/>
+        <v>7200</v>
+      </c>
+      <c r="F166" s="54"/>
+      <c r="G166" s="54"/>
+      <c r="H166" s="54"/>
+      <c r="I166" s="54"/>
+      <c r="J166" s="54"/>
+      <c r="K166" s="54"/>
+      <c r="L166" s="54"/>
+      <c r="M166" s="54"/>
+      <c r="N166" s="54"/>
+      <c r="O166" s="54"/>
+      <c r="P166" s="55"/>
+    </row>
+    <row r="167" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C167" s="61"/>
+      <c r="D167" s="53">
+        <v>15</v>
+      </c>
+      <c r="E167" s="55">
+        <f t="shared" si="114"/>
+        <v>6900</v>
+      </c>
+      <c r="F167" s="54"/>
+      <c r="G167" s="54"/>
+      <c r="H167" s="54"/>
+      <c r="I167" s="54"/>
+      <c r="J167" s="54"/>
+      <c r="K167" s="54"/>
+      <c r="L167" s="54"/>
+      <c r="M167" s="54"/>
+      <c r="N167" s="54"/>
+      <c r="O167" s="54"/>
+      <c r="P167" s="55"/>
+    </row>
+    <row r="168" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C168" s="61"/>
+      <c r="D168" s="75">
+        <v>20</v>
+      </c>
+      <c r="E168" s="34">
+        <f t="shared" si="114"/>
+        <v>6200</v>
+      </c>
+      <c r="F168" s="57"/>
+      <c r="G168" s="57"/>
+      <c r="H168" s="57"/>
+      <c r="I168" s="57"/>
+      <c r="J168" s="57"/>
+      <c r="K168" s="57"/>
+      <c r="L168" s="57"/>
+      <c r="M168" s="57"/>
+      <c r="N168" s="57"/>
+      <c r="O168" s="57"/>
+      <c r="P168" s="58"/>
+    </row>
+    <row r="169" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C169" s="61"/>
+    </row>
+    <row r="170" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C170" s="61"/>
+      <c r="D170" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E170" s="32"/>
+      <c r="F170" s="32"/>
+      <c r="G170" s="32"/>
+      <c r="H170" s="32"/>
+      <c r="I170" s="32"/>
+      <c r="J170" s="32"/>
+      <c r="K170" s="32"/>
+      <c r="L170" s="32"/>
+      <c r="M170" s="32"/>
+      <c r="N170" s="32"/>
+      <c r="O170" s="32"/>
+      <c r="P170" s="24"/>
+    </row>
+    <row r="171" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C171" s="61"/>
+      <c r="D171" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E171" s="38"/>
+      <c r="F171" s="38"/>
+      <c r="G171" s="38"/>
+      <c r="H171" s="38"/>
+      <c r="I171" s="38"/>
+      <c r="J171" s="38"/>
+      <c r="K171" s="38"/>
+      <c r="L171" s="38"/>
+      <c r="M171" s="38"/>
+      <c r="N171" s="38"/>
+      <c r="O171" s="38"/>
+      <c r="P171" s="8"/>
+    </row>
+    <row r="172" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C172" s="61"/>
+      <c r="D172" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E172" s="38">
+        <v>0</v>
+      </c>
+      <c r="F172" s="38"/>
+      <c r="G172" s="38"/>
+      <c r="H172" s="38"/>
+      <c r="I172" s="38"/>
+      <c r="J172" s="38"/>
+      <c r="K172" s="38"/>
+      <c r="L172" s="38"/>
+      <c r="M172" s="38"/>
+      <c r="N172" s="38"/>
+      <c r="O172" s="38"/>
+      <c r="P172" s="8"/>
+    </row>
+    <row r="173" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C173" s="61"/>
+      <c r="D173" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E173" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F173" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G173" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H173" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="I173" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J173" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K173" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L173" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M173" s="38"/>
+      <c r="N173" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="O173" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="P173" s="43" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="174" spans="3:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="C174" s="61"/>
+      <c r="D174" s="7">
+        <v>0</v>
+      </c>
+      <c r="E174" s="38">
+        <v>20</v>
+      </c>
+      <c r="F174" s="38">
+        <f>E174+G174-D174</f>
+        <v>20</v>
+      </c>
+      <c r="G174" s="38">
+        <v>0</v>
+      </c>
+      <c r="H174" s="37">
+        <f>$E$7*F174</f>
+        <v>1400</v>
+      </c>
+      <c r="I174" s="38">
+        <f>$E$6*IF(F174&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J174" s="38">
+        <f>D174*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K174" s="38">
+        <v>0</v>
+      </c>
+      <c r="L174" s="8">
+        <f>SUM(H174:K174)+$E$164</f>
+        <v>9600</v>
+      </c>
+      <c r="M174" s="38"/>
+      <c r="N174" s="7">
+        <f>IF(F174&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O174" s="38">
+        <f>IF(G174&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P174" s="8">
+        <f>IF(D174&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C175" s="61"/>
+      <c r="D175" s="7"/>
+      <c r="E175" s="38"/>
+      <c r="F175" s="38"/>
+      <c r="G175" s="38"/>
+      <c r="H175" s="38"/>
+      <c r="I175" s="38"/>
+      <c r="J175" s="38"/>
+      <c r="K175" s="38"/>
+      <c r="L175" s="38"/>
+      <c r="M175" s="38"/>
+      <c r="N175" s="38"/>
+      <c r="O175" s="38"/>
+      <c r="P175" s="8"/>
+    </row>
+    <row r="176" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C176" s="61"/>
+      <c r="D176" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E176" s="38"/>
+      <c r="F176" s="38"/>
+      <c r="G176" s="38"/>
+      <c r="H176" s="38"/>
+      <c r="I176" s="60"/>
+      <c r="J176" s="38"/>
+      <c r="K176" s="38"/>
+      <c r="L176" s="38"/>
+      <c r="M176" s="38"/>
+      <c r="N176" s="38"/>
+      <c r="O176" s="38"/>
+      <c r="P176" s="8"/>
+    </row>
+    <row r="177" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C177" s="61"/>
+      <c r="D177" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E177" s="38">
+        <v>5</v>
+      </c>
+      <c r="F177" s="38"/>
+      <c r="G177" s="38"/>
+      <c r="H177" s="38"/>
+      <c r="I177" s="38"/>
+      <c r="J177" s="38"/>
+      <c r="K177" s="38"/>
+      <c r="L177" s="38"/>
+      <c r="M177" s="38"/>
+      <c r="N177" s="38"/>
+      <c r="O177" s="38"/>
+      <c r="P177" s="8"/>
+    </row>
+    <row r="178" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C178" s="61"/>
+      <c r="D178" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E178" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F178" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G178" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H178" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="I178" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J178" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K178" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L178" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M178" s="38"/>
+      <c r="N178" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="O178" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="P178" s="43" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="179" spans="3:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="C179" s="61"/>
+      <c r="D179" s="7">
+        <v>0</v>
+      </c>
+      <c r="E179" s="38">
+        <v>20</v>
+      </c>
+      <c r="F179" s="38">
+        <f>E179+G179-D179</f>
+        <v>25</v>
+      </c>
+      <c r="G179" s="38">
+        <v>5</v>
+      </c>
+      <c r="H179" s="37">
+        <f>$E$7*F179</f>
+        <v>1750</v>
+      </c>
+      <c r="I179" s="38">
+        <f>$E$6*IF(F179&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J179" s="38">
+        <f>D179*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K179" s="38">
+        <v>0</v>
+      </c>
+      <c r="L179" s="8">
+        <f>SUM(H179:K179)+$E$165</f>
+        <v>9650</v>
+      </c>
+      <c r="M179" s="38"/>
+      <c r="N179" s="7">
+        <f>IF(F179&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O179" s="38">
+        <f>IF(G179&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P179" s="8">
+        <f>IF(D179&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C180" s="61"/>
+      <c r="D180" s="7"/>
+      <c r="E180" s="38"/>
+      <c r="F180" s="38"/>
+      <c r="G180" s="38"/>
+      <c r="H180" s="38"/>
+      <c r="I180" s="38"/>
+      <c r="J180" s="38"/>
+      <c r="K180" s="38"/>
+      <c r="L180" s="38"/>
+      <c r="M180" s="38"/>
+      <c r="N180" s="38"/>
+      <c r="O180" s="38"/>
+      <c r="P180" s="8"/>
+    </row>
+    <row r="181" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C181" s="61"/>
+      <c r="D181" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E181" s="38"/>
+      <c r="F181" s="38"/>
+      <c r="G181" s="38"/>
+      <c r="H181" s="38"/>
+      <c r="I181" s="38"/>
+      <c r="J181" s="38"/>
+      <c r="K181" s="38"/>
+      <c r="L181" s="38"/>
+      <c r="M181" s="38"/>
+      <c r="N181" s="38"/>
+      <c r="O181" s="38"/>
+      <c r="P181" s="8"/>
+    </row>
+    <row r="182" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C182" s="61"/>
+      <c r="D182" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E182" s="38">
+        <v>10</v>
+      </c>
+      <c r="F182" s="38"/>
+      <c r="G182" s="38"/>
+      <c r="H182" s="38"/>
+      <c r="I182" s="38"/>
+      <c r="J182" s="38"/>
+      <c r="K182" s="38"/>
+      <c r="L182" s="38"/>
+      <c r="M182" s="38"/>
+      <c r="N182" s="38"/>
+      <c r="O182" s="38"/>
+      <c r="P182" s="8"/>
+    </row>
+    <row r="183" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C183" s="61"/>
+      <c r="D183" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E183" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F183" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G183" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H183" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="I183" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J183" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K183" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L183" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M183" s="38"/>
+      <c r="N183" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="O183" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="P183" s="43" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="184" spans="3:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="C184" s="61"/>
+      <c r="D184" s="7">
+        <v>0</v>
+      </c>
+      <c r="E184" s="38">
+        <v>20</v>
+      </c>
+      <c r="F184" s="38">
+        <f>E184+G184-D184</f>
+        <v>30</v>
+      </c>
+      <c r="G184" s="38">
+        <v>10</v>
+      </c>
+      <c r="H184" s="37">
+        <f>$E$7*F184</f>
+        <v>2100</v>
+      </c>
+      <c r="I184" s="38">
+        <f>$E$6*IF(F184&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J184" s="38">
+        <f>D184*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K184" s="38">
+        <v>0</v>
+      </c>
+      <c r="L184" s="8">
+        <f>SUM(H184:K184)+$E$166</f>
+        <v>9700</v>
+      </c>
+      <c r="M184" s="38"/>
+      <c r="N184" s="7">
+        <f>IF(F184&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O184" s="38">
+        <f>IF(G184&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P184" s="8">
+        <f>IF(D184&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C185" s="61"/>
+      <c r="D185" s="7"/>
+      <c r="E185" s="38"/>
+      <c r="F185" s="38"/>
+      <c r="G185" s="38"/>
+      <c r="H185" s="38"/>
+      <c r="I185" s="38"/>
+      <c r="J185" s="38"/>
+      <c r="K185" s="38"/>
+      <c r="L185" s="38"/>
+      <c r="M185" s="38"/>
+      <c r="N185" s="38"/>
+      <c r="O185" s="38"/>
+      <c r="P185" s="8"/>
+    </row>
+    <row r="186" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="C186" s="61"/>
+      <c r="D186" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E186" s="38"/>
+      <c r="F186" s="38"/>
+      <c r="G186" s="38"/>
+      <c r="H186" s="38"/>
+      <c r="I186" s="38"/>
+      <c r="J186" s="38"/>
+      <c r="K186" s="38"/>
+      <c r="L186" s="38"/>
+      <c r="M186" s="38"/>
+      <c r="N186" s="38"/>
+      <c r="O186" s="38"/>
+      <c r="P186" s="8"/>
+    </row>
+    <row r="187" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C187" s="61"/>
+      <c r="D187" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E187" s="38">
+        <v>15</v>
+      </c>
+      <c r="F187" s="38"/>
+      <c r="G187" s="38"/>
+      <c r="H187" s="38"/>
+      <c r="I187" s="38"/>
+      <c r="J187" s="38"/>
+      <c r="K187" s="38"/>
+      <c r="L187" s="38"/>
+      <c r="M187" s="38"/>
+      <c r="N187" s="38"/>
+      <c r="O187" s="38"/>
+      <c r="P187" s="8"/>
+    </row>
+    <row r="188" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C188" s="61"/>
+      <c r="D188" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E188" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F188" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G188" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H188" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="I188" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J188" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K188" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L188" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M188" s="38"/>
+      <c r="N188" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="O188" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="P188" s="43" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="189" spans="3:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="D189" s="7">
+        <v>0</v>
+      </c>
+      <c r="E189" s="38">
+        <v>20</v>
+      </c>
+      <c r="F189" s="38">
+        <f>E189+G189-D189</f>
+        <v>35</v>
+      </c>
+      <c r="G189" s="38">
+        <v>15</v>
+      </c>
+      <c r="H189" s="37">
+        <f>$E$7*F189</f>
+        <v>2450</v>
+      </c>
+      <c r="I189" s="38">
+        <f>$E$6*IF(F189&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J189" s="38">
+        <f>D189*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K189" s="38">
+        <v>0</v>
+      </c>
+      <c r="L189" s="8">
+        <f>SUM(H189:K189)+E167</f>
+        <v>9750</v>
+      </c>
+      <c r="M189" s="38"/>
+      <c r="N189" s="7">
+        <f>IF(F189&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O189" s="38">
+        <f>IF(G189&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P189" s="8">
+        <f>IF(D189&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="D190" s="7"/>
+      <c r="E190" s="38"/>
+      <c r="F190" s="38"/>
+      <c r="G190" s="38"/>
+      <c r="H190" s="38"/>
+      <c r="I190" s="38"/>
+      <c r="J190" s="38"/>
+      <c r="K190" s="38"/>
+      <c r="L190" s="38"/>
+      <c r="M190" s="38"/>
+      <c r="N190" s="38"/>
+      <c r="O190" s="38"/>
+      <c r="P190" s="8"/>
+    </row>
+    <row r="191" spans="3:16" x14ac:dyDescent="0.35">
+      <c r="D191" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="E191" s="38"/>
+      <c r="F191" s="38"/>
+      <c r="G191" s="38"/>
+      <c r="H191" s="38"/>
+      <c r="I191" s="38"/>
+      <c r="J191" s="38"/>
+      <c r="K191" s="38"/>
+      <c r="L191" s="38"/>
+      <c r="M191" s="38"/>
+      <c r="N191" s="38"/>
+      <c r="O191" s="38"/>
+      <c r="P191" s="8"/>
+    </row>
+    <row r="192" spans="3:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D192" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E192" s="38">
+        <v>20</v>
+      </c>
+      <c r="F192" s="38"/>
+      <c r="G192" s="38"/>
+      <c r="H192" s="38"/>
+      <c r="I192" s="38"/>
+      <c r="J192" s="38"/>
+      <c r="K192" s="38"/>
+      <c r="L192" s="38"/>
+      <c r="M192" s="38"/>
+      <c r="N192" s="38"/>
+      <c r="O192" s="38"/>
+      <c r="P192" s="8"/>
+    </row>
+    <row r="193" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D193" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E193" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F193" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G193" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H193" s="40" t="s">
+        <v>44</v>
+      </c>
+      <c r="I193" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="J193" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="K193" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="L193" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M193" s="38"/>
+      <c r="N193" s="41" t="s">
+        <v>101</v>
+      </c>
+      <c r="O193" s="42" t="s">
+        <v>102</v>
+      </c>
+      <c r="P193" s="43" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="194" spans="4:16" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="D194" s="7">
+        <v>0</v>
+      </c>
+      <c r="E194" s="38">
+        <v>20</v>
+      </c>
+      <c r="F194" s="74">
+        <f>E194+G194-D194</f>
+        <v>40</v>
+      </c>
+      <c r="G194" s="38">
+        <v>20</v>
+      </c>
+      <c r="H194" s="37">
+        <f>$E$7*F194</f>
+        <v>2800</v>
+      </c>
+      <c r="I194" s="38">
+        <f>$E$6*IF(F194&gt;0,1,0)</f>
+        <v>400</v>
+      </c>
+      <c r="J194" s="38">
+        <f>D194*$E$9</f>
+        <v>0</v>
+      </c>
+      <c r="K194" s="38">
+        <v>0</v>
+      </c>
+      <c r="L194" s="36">
+        <f>SUM(H194:K194)+E168</f>
+        <v>9400</v>
+      </c>
+      <c r="M194" s="38"/>
+      <c r="N194" s="7">
+        <f>IF(F194&lt;=$E$4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O194" s="38">
+        <f>IF(G194&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P194" s="8">
+        <f>IF(D194&lt;=$E$8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D195" s="7"/>
+      <c r="E195" s="38"/>
+      <c r="F195" s="38"/>
+      <c r="G195" s="38"/>
+      <c r="H195" s="38"/>
+      <c r="I195" s="38"/>
+      <c r="J195" s="38"/>
+      <c r="K195" s="38"/>
+      <c r="L195" s="38"/>
+      <c r="M195" s="38"/>
+      <c r="N195" s="38"/>
+      <c r="O195" s="38"/>
+      <c r="P195" s="8"/>
+    </row>
+    <row r="196" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D196" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E196" s="24"/>
+      <c r="F196" s="38"/>
+      <c r="G196" s="38"/>
+      <c r="H196" s="38"/>
+      <c r="I196" s="38"/>
+      <c r="J196" s="38"/>
+      <c r="K196" s="38"/>
+      <c r="L196" s="38"/>
+      <c r="M196" s="38"/>
+      <c r="N196" s="38"/>
+      <c r="O196" s="38"/>
+      <c r="P196" s="8"/>
+    </row>
+    <row r="197" spans="4:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D197" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E197" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F197" s="38"/>
+      <c r="G197" s="38"/>
+      <c r="H197" s="38"/>
+      <c r="I197" s="38"/>
+      <c r="J197" s="38"/>
+      <c r="K197" s="38"/>
+      <c r="L197" s="38"/>
+      <c r="M197" s="38"/>
+      <c r="N197" s="38"/>
+      <c r="O197" s="38"/>
+      <c r="P197" s="8"/>
+    </row>
+    <row r="198" spans="4:16" ht="15.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D198" s="72">
+        <v>20</v>
+      </c>
+      <c r="E198" s="73">
+        <f>MIN(L174,L179,L184,L189,L194)</f>
+        <v>9400</v>
+      </c>
+      <c r="F198" s="21"/>
+      <c r="G198" s="21"/>
+      <c r="H198" s="21"/>
+      <c r="I198" s="21"/>
+      <c r="J198" s="21"/>
+      <c r="K198" s="21"/>
+      <c r="L198" s="21"/>
+      <c r="M198" s="21"/>
+      <c r="N198" s="21"/>
+      <c r="O198" s="21"/>
+      <c r="P198" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98968E66-15E9-49A0-B7CF-F04F754C98DA}">
+  <dimension ref="C2:M27"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.08984375" customWidth="1"/>
+    <col min="12" max="12" width="7.26953125" customWidth="1"/>
+    <col min="13" max="13" width="5.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="H3" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="24"/>
+    </row>
+    <row r="4" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>109</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I4" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="8"/>
+    </row>
+    <row r="5" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>110</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="38">
+        <v>0</v>
+      </c>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="8"/>
+    </row>
+    <row r="6" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H6" s="7">
+        <v>1</v>
+      </c>
+      <c r="I6" s="38">
+        <v>2.8</v>
+      </c>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="8"/>
+    </row>
+    <row r="7" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="H7" s="7">
+        <v>2</v>
+      </c>
+      <c r="I7" s="38">
+        <v>3.3</v>
+      </c>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="8"/>
+    </row>
+    <row r="8" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="H8" s="7">
+        <v>3</v>
+      </c>
+      <c r="I8" s="38">
+        <v>3.7</v>
+      </c>
+      <c r="J8" s="38"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="H9" s="7">
+        <v>4</v>
+      </c>
+      <c r="I9" s="38">
+        <v>4</v>
+      </c>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="8"/>
+    </row>
+    <row r="10" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="H10" s="7"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="8"/>
+    </row>
+    <row r="11" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H11" s="7"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="8"/>
+    </row>
+    <row r="12" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C12" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="32"/>
+      <c r="E12" s="24"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="8"/>
+    </row>
+    <row r="13" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C13" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D13" s="38">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="8"/>
+    </row>
+    <row r="14" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C14" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="I14" s="38">
+        <v>4</v>
+      </c>
+      <c r="J14" s="38">
+        <v>3</v>
+      </c>
+      <c r="K14" s="38">
+        <v>2</v>
+      </c>
+      <c r="L14" s="38">
+        <v>1</v>
+      </c>
+      <c r="M14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C15" s="7">
+        <v>0</v>
+      </c>
+      <c r="D15" s="38">
+        <f>4-C15</f>
+        <v>4</v>
+      </c>
+      <c r="E15" s="8">
+        <v>5</v>
+      </c>
+      <c r="H15" s="7">
+        <v>0</v>
+      </c>
+      <c r="I15" s="88">
+        <f>E15</f>
+        <v>5</v>
+      </c>
+      <c r="J15" s="90">
+        <f>I5+E16</f>
+        <v>4.2</v>
+      </c>
+      <c r="K15" s="92">
+        <f>E17</f>
+        <v>3</v>
+      </c>
+      <c r="L15" s="94">
+        <f>E18</f>
+        <v>1.7</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C16" s="7">
+        <v>1</v>
+      </c>
+      <c r="D16" s="38">
+        <f t="shared" ref="D16:D19" si="0">4-C16</f>
+        <v>3</v>
+      </c>
+      <c r="E16" s="8">
+        <v>4.2</v>
+      </c>
+      <c r="H16" s="7">
+        <v>1</v>
+      </c>
+      <c r="I16" s="38"/>
+      <c r="J16" s="88">
+        <f>I6+E16</f>
+        <v>7</v>
+      </c>
+      <c r="K16" s="90">
+        <f>I6+E17</f>
+        <v>5.8</v>
+      </c>
+      <c r="L16" s="96">
+        <f>I6+E18</f>
+        <v>4.5</v>
+      </c>
+      <c r="M16" s="95">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C17" s="7">
+        <v>2</v>
+      </c>
+      <c r="D17" s="38">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E17" s="8">
+        <v>3</v>
+      </c>
+      <c r="H17" s="7">
+        <v>2</v>
+      </c>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="88">
+        <f>I7+E17</f>
+        <v>6.3</v>
+      </c>
+      <c r="L17" s="90">
+        <f>I7+E18</f>
+        <v>5</v>
+      </c>
+      <c r="M17" s="93">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C18" s="7">
+        <v>3</v>
+      </c>
+      <c r="D18" s="38">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E18" s="52">
+        <v>1.7</v>
+      </c>
+      <c r="H18" s="7">
+        <v>3</v>
+      </c>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="88">
+        <f>I8+E18</f>
+        <v>5.4</v>
+      </c>
+      <c r="M18" s="91">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C19" s="9">
+        <v>4</v>
+      </c>
+      <c r="D19" s="21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="10">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9">
+        <v>4</v>
+      </c>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="89">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="H21" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="24"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" t="s">
+        <v>119</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I22" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="J22" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="H23" s="7">
+        <v>0</v>
+      </c>
+      <c r="I23" s="38">
+        <v>0</v>
+      </c>
+      <c r="J23" s="38">
+        <f>4-H23</f>
+        <v>4</v>
+      </c>
+      <c r="K23" s="8">
+        <f>I23+MAX(I15,J16,K17,L18,M19)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C24" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="H24" s="7">
+        <v>1</v>
+      </c>
+      <c r="I24" s="38">
+        <v>1.5</v>
+      </c>
+      <c r="J24" s="38">
+        <f>4-H24</f>
+        <v>3</v>
+      </c>
+      <c r="K24" s="8">
+        <f>I24+MAX(J15,K16,L17,M18)</f>
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="C25" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="H25" s="7">
+        <v>2</v>
+      </c>
+      <c r="I25" s="38">
+        <v>3.5</v>
+      </c>
+      <c r="J25" s="38">
+        <f>4-H25</f>
+        <v>2</v>
+      </c>
+      <c r="K25" s="52">
+        <f>I25+MAX(K15,L16,M17)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.35">
+      <c r="H26" s="7">
+        <v>3</v>
+      </c>
+      <c r="I26" s="38">
+        <v>5</v>
+      </c>
+      <c r="J26" s="38">
+        <f>4-H26</f>
+        <v>1</v>
+      </c>
+      <c r="K26" s="8">
+        <f>I26+MAX(L15,M16)</f>
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H27" s="9">
+        <v>4</v>
+      </c>
+      <c r="I27" s="21">
+        <v>6</v>
+      </c>
+      <c r="J27" s="21">
+        <f>4-H27</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="10">
+        <f>I27+M15</f>
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>